--- a/data-source/ESTOQUETRANSFER.xlsx
+++ b/data-source/ESTOQUETRANSFER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/TRANSFER-ANALISE/data-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BFC21E3A-6DA0-4D0A-9B2A-B3A115A5BCBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{20405EE4-7847-4583-ADA9-6FB66CEB9340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B23CEC38-E292-4C09-AB0F-363D0F097CA9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,10 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="133">
-  <si>
-    <t/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="131">
   <si>
     <t>Produto</t>
   </si>
@@ -51,391 +48,388 @@
     <t>Qtd.física</t>
   </si>
   <si>
+    <t>TRANSF PARC EC150 FURTA COR 201 - ECOTEX/MLT COL MOD 99-5 AM</t>
+  </si>
+  <si>
+    <t>TRANSFER PARCIAL EC150 AZUL 014 - ECOTEX</t>
+  </si>
+  <si>
+    <t>TRANSFER PARCIAL EC150 ROXO 001 - ECOTEX</t>
+  </si>
+  <si>
+    <t>TRANSFER PARCIAL EC150 OURO 004 - ECOTEX</t>
+  </si>
+  <si>
+    <t>TRANSFER PARCIAL MX50 919F ROSE -CROWN ROLL</t>
+  </si>
+  <si>
+    <t>TRANSFER PARCIAL MX50015F RAINBOW - CROWN ROLL</t>
+  </si>
+  <si>
+    <t>TRANSFER FILM LEOPARD - AMERICA ASIA</t>
+  </si>
+  <si>
+    <t>CARTEGE/IRONING</t>
+  </si>
+  <si>
+    <t>CARTEGE ACETINADO/SEMI FOSCO</t>
+  </si>
+  <si>
+    <t>TRANSFER MX50 135 OURO LADY - CROWN ROLL</t>
+  </si>
+  <si>
+    <t>TRANSFER COBRA LUXO - AMERICA ASIA</t>
+  </si>
+  <si>
+    <t>TRANSFER PARCIAL HOLOGRAFICO OURO CONFETI/SOARES</t>
+  </si>
+  <si>
+    <t>TRANSFER PARCIAL HOLOGRAFICO PRATA CONFETI/GLOBAL/ANAMA</t>
+  </si>
+  <si>
+    <t>FILME SMELL TEX PU 600</t>
+  </si>
+  <si>
+    <t>TRANSFER PARCIAL  MX50651F  CHUMBO - CROWN ROLL</t>
+  </si>
+  <si>
+    <t>TRANSFER PARCIAL HOLOGRAFICO PRATA GLOBAL/TRANSFER 305</t>
+  </si>
+  <si>
+    <t>TRANSFER PARCIAL HOLOGRAFICO PRATA CRISTAL JUMBO/GLOBAL/ANAM</t>
+  </si>
+  <si>
+    <t>TRANSFER PARCIAL HOLOGRAFICO PINK CONFETI/GLOBAL/ANAMA</t>
+  </si>
+  <si>
+    <t>TRANSFER  MX50888F VERDE BANDEIRA - CROWN ROLL</t>
+  </si>
+  <si>
+    <t>TRANSFER PARCIAL MX50 100 F PRATA CROWN/UNIFOILS</t>
+  </si>
+  <si>
+    <t>TRANSFER PARCIAL MX50 587F SKY UNIFOILS</t>
+  </si>
+  <si>
+    <t>TRANSFER PARCIAL MX50 702F BABY PINK UNIFOILS/CROWN</t>
+  </si>
+  <si>
+    <t>TRANSFER PARCIAL MX50 935F COBRE UNIFOILS/CROWN</t>
+  </si>
+  <si>
+    <t>TRANSFER TOTAL METALIC FILM FULL PINK HBZP-1151B AMERICA ASI</t>
+  </si>
+  <si>
+    <t>TRANSFER PARCIAL METALIC PURPLE 627 AMERICA ASIA</t>
+  </si>
+  <si>
+    <t>TRANSFER PARCIAL METALIC GREEN 8K AMERICA ASIA</t>
+  </si>
+  <si>
+    <t>TRANSFER PARCIAL METALIC DARK PURPLE K AMERICA ASIA</t>
+  </si>
+  <si>
+    <t>TRANSFER PARCIAL METALIC COOPER 627 AMERICA ASIA</t>
+  </si>
+  <si>
+    <t>TRANSFER PARCIAL  MX50 121F OURO BRANCO - MERCOFOILS/UNIFOIL</t>
+  </si>
+  <si>
+    <t>TRANSFER EC150 OLEO 210 - ECOTEX</t>
+  </si>
+  <si>
+    <t>TRANSFER PARCIAL MX50 714F PINK UNIFOILS/CROWN</t>
+  </si>
+  <si>
+    <t>TRANSFER PARCIAL MX50 990F CAFÉ CROWN/UNIFOILS</t>
+  </si>
+  <si>
+    <t>TRANSFER PARCIAL MX50 991F NIGHT SKY UNIFOILS</t>
+  </si>
+  <si>
+    <t>TRANSFER PARCIAL METALIC BLUE 553 AMERICA ASIA(METAL SOFT BA</t>
+  </si>
+  <si>
+    <t>TRANSFER TOTAL METALIC FILM GRAFITE QT-339A - AMERICA ASIA</t>
+  </si>
+  <si>
+    <t>TRANSFER TOTAL METALIC FILM GOLD QT-HB-056A - AMERICA ASIA</t>
+  </si>
+  <si>
+    <t>TRANSFER TOTAL METALIC FILM SILVER QT-001A - AMERICA ASIA</t>
+  </si>
+  <si>
+    <t>TRANSFER TOTAL METALIC FILM ROSE GOLD QT-468A - AMERICA ASIA</t>
+  </si>
+  <si>
+    <t>TRANSFOIL MINITAIPAN</t>
+  </si>
+  <si>
+    <t>TRANSFER PARCIAL FANTASY CAMALEÃO - AMÉRICA ASIA</t>
+  </si>
+  <si>
+    <t>TRANSFER TOTAL METALIC FILM BLUE QT-226A - AMERICA ASIA</t>
+  </si>
+  <si>
+    <t>TRANSFER TOTAL METALIC FILM PINK QT-277A - AMERICA ASIA</t>
+  </si>
+  <si>
+    <t>TRANSFER TOTAL OURO - GLOBAL</t>
+  </si>
+  <si>
+    <t>TRANSFER EC142 PRATA 001</t>
+  </si>
+  <si>
+    <t>TRANSFER EC142 COBRE 494</t>
+  </si>
+  <si>
+    <t>TRANSFER LAMINA ORBC - PALAGI</t>
+  </si>
+  <si>
+    <t>TRANSFOIL SNAKE 881 - TRANSPARENTE</t>
+  </si>
+  <si>
+    <t>TRANSFER TOTAL METALIC FILM PEWTER QT-110A - AMERICA ASIA</t>
+  </si>
+  <si>
+    <t>TRANSFER ECOTEX LILAS</t>
+  </si>
+  <si>
+    <t>TRANSFER UNITRANS 104 - PALAGI</t>
+  </si>
+  <si>
+    <t>STARTLIGHT FILM - SILVER (GLITTER FILM)</t>
+  </si>
+  <si>
+    <t>STARTLIGHT FILM - BLACK (GLITTER MP)</t>
+  </si>
+  <si>
+    <t>STARTLIGHT FILM - LT GOLD (GLITTER MP)</t>
+  </si>
+  <si>
+    <t>STARTLIGHT FILM - ROSE GOLD (GLITTER MP)</t>
+  </si>
+  <si>
+    <t>TRANSFER LAMINA SILVER - PALAGI</t>
+  </si>
+  <si>
+    <t>TRANSFER HOLO STAR</t>
+  </si>
+  <si>
+    <t>TRANSFER LAMINA BR2 BRONZE - PALAGI</t>
+  </si>
+  <si>
+    <t>FILME TPU 200 - POLLIBOX</t>
+  </si>
+  <si>
+    <t>TRANSFER TOTAL METALIC FILM QT-347A LIGHT ROSE</t>
+  </si>
+  <si>
+    <t>GLITTER FILM - MULTI WHITE</t>
+  </si>
+  <si>
+    <t>TRANSFER LAMINA METAL BLACK - PALAGI</t>
+  </si>
+  <si>
+    <t>TRANSFER LACCA NERO - Z</t>
+  </si>
+  <si>
+    <t>TRANSFER UNITRANS TR - 147</t>
+  </si>
+  <si>
+    <t>TRANSFER UNITRANS TR - 176</t>
+  </si>
+  <si>
+    <t>TRANSFER LAMINA BR SC</t>
+  </si>
+  <si>
+    <t>TRANSFER LAMINA CF</t>
+  </si>
+  <si>
+    <t>QT-120A METALIC FILM (FULL TRANSFER) - RUBY</t>
+  </si>
+  <si>
+    <t>TRANSFER LAMINA CAMALEÃO V/R - PALAGI</t>
+  </si>
+  <si>
+    <t>TRANSFER LAMINA TM - PALAGI</t>
+  </si>
+  <si>
+    <t>TRANSFER LAMINA PL 2 - PALAGI</t>
+  </si>
+  <si>
+    <t>TRANSFER UNITRANS 145 TR - PALAGI</t>
+  </si>
+  <si>
+    <t>TRANSFER UNI B006 JEWEL PL2 - PALAGI</t>
+  </si>
+  <si>
+    <t>TRANSFER UNITRANS JEWEL I009RE - PALAGI</t>
+  </si>
+  <si>
+    <t>FILM NEW 2023 STYLE 10#</t>
+  </si>
+  <si>
+    <t>TRANSFER UNITRANS 118 TR - PALAGI</t>
+  </si>
+  <si>
+    <t>TRANSFER LAMINA OURO LIGHT - PALAGI</t>
+  </si>
+  <si>
+    <t>TRANSFER LAMINA CROMO - PALAGI</t>
+  </si>
+  <si>
+    <t>TRANSFER TOTAL METALIC FILM MARINE QT-331A - AMERICA ASIA</t>
+  </si>
+  <si>
+    <t>TRANSFER TOTAL METALIC FILM GREEN QT-238A - AMERICA ASIA</t>
+  </si>
+  <si>
+    <t>TRANSFER LAMINA CRISTAL IRIS - PALAGI</t>
+  </si>
+  <si>
+    <t>TERMOFILME ELASTOMELT 55L - ELASTOSUL</t>
+  </si>
+  <si>
+    <t>TRANSFER LAMINA RAINBOW 3-2 - PALAGI</t>
+  </si>
+  <si>
+    <t>TRANSFER UNITRANS E032 TR 1,60 LARG</t>
+  </si>
+  <si>
+    <t>TRANSFER UNITRANS 363 TR</t>
+  </si>
+  <si>
+    <t>TRANSFER 59134 NEW</t>
+  </si>
+  <si>
+    <t>CARTEGE IRONING FILM 0,1MM</t>
+  </si>
+  <si>
+    <t>TRASNFER LAMINA OT - PALAGI</t>
+  </si>
+  <si>
+    <t>TRANSFER LAMINA LIGHT SUN</t>
+  </si>
+  <si>
+    <t>TRANSFER LAMINA DOURADO 1,5</t>
+  </si>
+  <si>
+    <t>TRANSFER LAMINA GRADIENTE - PALAGI</t>
+  </si>
+  <si>
+    <t>TRANSFER LAMINA HOL LASER AG</t>
+  </si>
+  <si>
+    <t>TRANSFER LAMINA LASER ROSE - PALAGI</t>
+  </si>
+  <si>
+    <t>TRANSFER LAMINA GOLD 5910 - PA</t>
+  </si>
+  <si>
+    <t>TRANSFER UNITRANS 203 TR 1,49 LARG</t>
+  </si>
+  <si>
+    <t>TRANSFER CRISTAL FOIL FLOATER 1,50 LARG</t>
+  </si>
+  <si>
+    <t>TRANSFER CRISTAL FOIL MINI STAR 1,50 LARG</t>
+  </si>
+  <si>
+    <t>TRANSFER CRISTAL FOIL RISCADO 1,50 LARG</t>
+  </si>
+  <si>
+    <t>TRANSFER UNITRANS U288 XH 1,60 LARG</t>
+  </si>
+  <si>
+    <t>TRANSFER MULTI COLOR CONFETI 1,50 LARG</t>
+  </si>
+  <si>
+    <t>TRANSFER 99-5-4 PARCIAL FOIL - SILVER</t>
+  </si>
+  <si>
+    <t>TRANSFER 99-5-4 PARCIAL FOIL - GOLD</t>
+  </si>
+  <si>
+    <t>TRANSFER 99-5-4 PARCIAL FILM - GRAPHITE</t>
+  </si>
+  <si>
+    <t>TRANSFER 99-5-4 PARCIAL FILM - ROSE GOLD</t>
+  </si>
+  <si>
+    <t>TRANSFER LAM LASER ROSE NEW 2</t>
+  </si>
+  <si>
+    <t>TRANSFER 99-5-4 PARCIAL COFFEE</t>
+  </si>
+  <si>
+    <t>TRANSFER LAMINA HOL LASER NERO</t>
+  </si>
+  <si>
+    <t>TRANSFER LAMINA LASER ORO NEW</t>
+  </si>
+  <si>
+    <t>TRANSFER UNITRANS 396 TR</t>
+  </si>
+  <si>
+    <t>FOLHAS PARA MARCAR A FERRO EM BOBINAS MX50 135F - OURO LADY</t>
+  </si>
+  <si>
+    <t>UNITRANS SERPENTE</t>
+  </si>
+  <si>
+    <t>TRANSFER UNITRANS 185 - PALAGI</t>
+  </si>
+  <si>
+    <t>TRANSFER UNITRANS 489 - PALAGI</t>
+  </si>
+  <si>
+    <t>TRANSFER UNITRANS 115 - PALAGI</t>
+  </si>
+  <si>
+    <t>QT-200A FULL TRANSFER - CAFÉ</t>
+  </si>
+  <si>
+    <t>QT-077A FULL TRANSFER - WHISKY</t>
+  </si>
+  <si>
     <t>Grupo</t>
   </si>
   <si>
     <t>Familia</t>
   </si>
   <si>
-    <t>TRANSF PARC EC150 FURTA COR 201 - ECOTEX/MLT COL MOD 99-5 AM</t>
-  </si>
-  <si>
-    <t>TRANSFER PARCIAL EC150 AZUL 014 - ECOTEX</t>
-  </si>
-  <si>
-    <t>TRANSFER PARCIAL EC150 ROXO 001 - ECOTEX</t>
-  </si>
-  <si>
-    <t>TRANSFER PARCIAL EC150 OURO 004 - ECOTEX</t>
-  </si>
-  <si>
-    <t>TRANSFER PARCIAL MX50 919F ROSE -CROWN ROLL</t>
-  </si>
-  <si>
-    <t>TRANSFER PARCIAL MX50015F RAINBOW - CROWN ROLL</t>
-  </si>
-  <si>
-    <t>TRANSFER FILM LEOPARD - AMERICA ASIA</t>
-  </si>
-  <si>
-    <t>CARTEGE/IRONING</t>
-  </si>
-  <si>
-    <t>CARTEGE ACETINADO/SEMI FOSCO</t>
-  </si>
-  <si>
-    <t>TRANSFER MX50 135 OURO LADY - CROWN ROLL</t>
-  </si>
-  <si>
-    <t>TRANSFER COBRA LUXO - AMERICA ASIA</t>
-  </si>
-  <si>
-    <t>TRANSFER PARCIAL HOLOGRAFICO OURO CONFETI/SOARES</t>
-  </si>
-  <si>
-    <t>TRANSFER PARCIAL HOLOGRAFICO PRATA CONFETI/GLOBAL/ANAMA</t>
-  </si>
-  <si>
-    <t>FILME SMELL TEX PU 600</t>
-  </si>
-  <si>
-    <t>TRANSFER PARCIAL  MX50651F  CHUMBO - CROWN ROLL</t>
-  </si>
-  <si>
-    <t>TRANSFER PARCIAL HOLOGRAFICO PRATA GLOBAL/TRANSFER 305</t>
-  </si>
-  <si>
-    <t>TRANSFER PARCIAL HOLOGRAFICO PRATA CRISTAL JUMBO/GLOBAL/ANAM</t>
-  </si>
-  <si>
-    <t>TRANSFER PARCIAL HOLOGRAFICO PINK CONFETI/GLOBAL/ANAMA</t>
-  </si>
-  <si>
-    <t>TRANSFER  MX50888F VERDE BANDEIRA - CROWN ROLL</t>
-  </si>
-  <si>
-    <t>TRANSFER PARCIAL MX50 100 F PRATA CROWN/UNIFOILS</t>
-  </si>
-  <si>
-    <t>TRANSFER PARCIAL MX50 587F SKY UNIFOILS</t>
-  </si>
-  <si>
-    <t>TRANSFER PARCIAL MX50 702F BABY PINK UNIFOILS/CROWN</t>
-  </si>
-  <si>
-    <t>TRANSFER PARCIAL MX50 935F COBRE UNIFOILS/CROWN</t>
-  </si>
-  <si>
-    <t>TRANSFER TOTAL METALIC FILM FULL PINK HBZP-1151B AMERICA ASI</t>
-  </si>
-  <si>
-    <t>TRANSFER PARCIAL METALIC PURPLE 627 AMERICA ASIA</t>
-  </si>
-  <si>
-    <t>TRANSFER PARCIAL METALIC GREEN 8K AMERICA ASIA</t>
-  </si>
-  <si>
-    <t>TRANSFER PARCIAL METALIC DARK PURPLE K AMERICA ASIA</t>
-  </si>
-  <si>
-    <t>TRANSFER PARCIAL METALIC COOPER 627 AMERICA ASIA</t>
-  </si>
-  <si>
-    <t>TRANSFER PARCIAL  MX50 121F OURO BRANCO - MERCOFOILS/UNIFOIL</t>
-  </si>
-  <si>
-    <t>TRANSFER EC150 OLEO 210 - ECOTEX</t>
-  </si>
-  <si>
-    <t>TRANSFER PARCIAL MX50 714F PINK UNIFOILS/CROWN</t>
-  </si>
-  <si>
-    <t>TRANSFER PARCIAL MX50 990F CAFÉ CROWN/UNIFOILS</t>
-  </si>
-  <si>
-    <t>TRANSFER PARCIAL MX50 991F NIGHT SKY UNIFOILS</t>
-  </si>
-  <si>
-    <t>TRANSFER PARCIAL METALIC BLUE 553 AMERICA ASIA(METAL SOFT BA</t>
-  </si>
-  <si>
-    <t>TRANSFER TOTAL METALIC FILM GRAFITE QT-339A - AMERICA ASIA</t>
-  </si>
-  <si>
-    <t>TRANSFER TOTAL METALIC FILM GOLD QT-HB-056A - AMERICA ASIA</t>
-  </si>
-  <si>
-    <t>TRANSFER TOTAL METALIC FILM SILVER QT-001A - AMERICA ASIA</t>
-  </si>
-  <si>
-    <t>TRANSFER TOTAL METALIC FILM ROSE GOLD QT-468A - AMERICA ASIA</t>
-  </si>
-  <si>
-    <t>TRANSFOIL MINITAIPAN</t>
-  </si>
-  <si>
-    <t>TRANSFER PARCIAL FANTASY CAMALEÃO - AMÉRICA ASIA</t>
-  </si>
-  <si>
-    <t>TRANSFER TOTAL METALIC FILM BLUE QT-226A - AMERICA ASIA</t>
-  </si>
-  <si>
-    <t>TRANSFER TOTAL METALIC FILM PINK QT-277A - AMERICA ASIA</t>
-  </si>
-  <si>
-    <t>TRANSFER TOTAL OURO - GLOBAL</t>
-  </si>
-  <si>
-    <t>TRANSFER EC142 PRATA 001</t>
-  </si>
-  <si>
-    <t>TRANSFER EC142 COBRE 494</t>
-  </si>
-  <si>
-    <t>TRANSFER LAMINA ORBC - PALAGI</t>
-  </si>
-  <si>
-    <t>TRANSFOIL SNAKE 881 - TRANSPARENTE</t>
-  </si>
-  <si>
-    <t>TRANSFER TOTAL METALIC FILM PEWTER QT-110A - AMERICA ASIA</t>
-  </si>
-  <si>
-    <t>TRANSFER ECOTEX LILAS</t>
-  </si>
-  <si>
-    <t>TRANSFER UNITRANS 104 - PALAGI</t>
-  </si>
-  <si>
-    <t>STARTLIGHT FILM - SILVER (GLITTER FILM)</t>
-  </si>
-  <si>
-    <t>STARTLIGHT FILM - BLACK (GLITTER MP)</t>
-  </si>
-  <si>
-    <t>STARTLIGHT FILM - LT GOLD (GLITTER MP)</t>
-  </si>
-  <si>
-    <t>STARTLIGHT FILM - ROSE GOLD (GLITTER MP)</t>
-  </si>
-  <si>
-    <t>TRANSFER LAMINA SILVER - PALAGI</t>
-  </si>
-  <si>
-    <t>TRANSFER HOLO STAR</t>
-  </si>
-  <si>
-    <t>TRANSFER LAMINA BR2 BRONZE - PALAGI</t>
-  </si>
-  <si>
-    <t>FILME TPU 200 - POLLIBOX</t>
-  </si>
-  <si>
-    <t>TRANSFER TOTAL METALIC FILM QT-347A LIGHT ROSE</t>
-  </si>
-  <si>
-    <t>GLITTER FILM - MULTI WHITE</t>
-  </si>
-  <si>
-    <t>TRANSFER LAMINA METAL BLACK - PALAGI</t>
-  </si>
-  <si>
-    <t>TRANSFER LACCA NERO - Z</t>
-  </si>
-  <si>
-    <t>TRANSFER UNITRANS TR - 147</t>
-  </si>
-  <si>
-    <t>TRANSFER UNITRANS TR - 176</t>
-  </si>
-  <si>
-    <t>TRANSFER LAMINA BR SC</t>
-  </si>
-  <si>
-    <t>TRANSFER LAMINA CF</t>
-  </si>
-  <si>
-    <t>QT-120A METALIC FILM (FULL TRANSFER) - RUBY</t>
-  </si>
-  <si>
-    <t>QT-467A METALIC FILM (FULL TRANSFER) - BRONZE</t>
-  </si>
-  <si>
-    <t>TRANSFER LAMINA CAMALEÃO V/R - PALAGI</t>
-  </si>
-  <si>
-    <t>TRANSFER LAMINA TM - PALAGI</t>
-  </si>
-  <si>
-    <t>TRANSFER LAMINA PL 2 - PALAGI</t>
-  </si>
-  <si>
-    <t>TRANSFER UNITRANS 145 TR - PALAGI</t>
-  </si>
-  <si>
-    <t>TRANSFER UNI B006 JEWEL PL2 - PALAGI</t>
-  </si>
-  <si>
-    <t>TRANSFER UNITRANS JEWEL I009RE - PALAGI</t>
-  </si>
-  <si>
-    <t>FILM NEW 2023 STYLE 10#</t>
-  </si>
-  <si>
-    <t>TRANSFER UNITRANS 118 TR - PALAGI</t>
-  </si>
-  <si>
-    <t>TRANSFER LAMINA OURO LIGHT - PALAGI</t>
-  </si>
-  <si>
-    <t>TRANSFER LAMINA CROMO - PALAGI</t>
-  </si>
-  <si>
-    <t>TRANSFER TOTAL METALIC FILM MARINE QT-331A - AMERICA ASIA</t>
-  </si>
-  <si>
-    <t>TRANSFER TOTAL METALIC FILM GREEN QT-238A - AMERICA ASIA</t>
-  </si>
-  <si>
-    <t>TRANSFER LAMINA CRISTAL IRIS - PALAGI</t>
-  </si>
-  <si>
-    <t>TERMOFILME ELASTOMELT 55L - ELASTOSUL</t>
-  </si>
-  <si>
-    <t>TRANSFER LAMINA RAINBOW 3-2 - PALAGI</t>
-  </si>
-  <si>
-    <t>TRANSFER UNITRANS E032 TR 1,60 LARG</t>
-  </si>
-  <si>
-    <t>TRANSFER UNITRANS 363 TR</t>
-  </si>
-  <si>
-    <t>TRANSFER 59134 NEW</t>
-  </si>
-  <si>
-    <t>CARTEGE IRONING FILM 0,1MM</t>
-  </si>
-  <si>
-    <t>TRASNFER LAMINA OT - PALAGI</t>
-  </si>
-  <si>
-    <t>TRANSFER LAMINA LIGHT SUN</t>
-  </si>
-  <si>
-    <t>TRANSFER LAMINA DOURADO 1,5</t>
-  </si>
-  <si>
-    <t>TRANSFER LAMINA GRADIENTE - PALAGI</t>
-  </si>
-  <si>
-    <t>TRANSFER LAMINA HOL LASER AG</t>
-  </si>
-  <si>
-    <t>TRANSFER LAMINA LASER ROSE - PALAGI</t>
-  </si>
-  <si>
-    <t>TRANSFER LAMINA GOLD 5910 - PA</t>
-  </si>
-  <si>
-    <t>TRANSFER UNITRANS 203 TR 1,49 LARG</t>
-  </si>
-  <si>
-    <t>TRANSFER CRISTAL FOIL FLOATER 1,50 LARG</t>
-  </si>
-  <si>
-    <t>TRANSFER CRISTAL FOIL MINI STAR 1,50 LARG</t>
-  </si>
-  <si>
-    <t>TRANSFER CRISTAL FOIL RISCADO 1,50 LARG</t>
-  </si>
-  <si>
-    <t>TRANSFER UNITRANS U288 XH 1,60 LARG</t>
-  </si>
-  <si>
-    <t>TRANSFER MULTI COLOR CONFETI 1,50 LARG</t>
-  </si>
-  <si>
-    <t>TRANSFER 99-5-4 PARCIAL FOIL - SILVER</t>
-  </si>
-  <si>
-    <t>TRANSFER 99-5-4 PARCIAL FOIL - LT GOLD</t>
-  </si>
-  <si>
-    <t>TRANSFER 99-5-4 PARCIAL FOIL - GOLD</t>
-  </si>
-  <si>
-    <t>TRANSFER 99-5-4 PARCIAL FILM - GRAPHITE</t>
-  </si>
-  <si>
-    <t>TRANSFER 99-5-4 PARCIAL FILM - ROSE GOLD</t>
-  </si>
-  <si>
-    <t>TRANSFER LAM LASER ROSE NEW 2</t>
-  </si>
-  <si>
-    <t>TRANSFER 99-5-4 PARCIAL COFFEE</t>
-  </si>
-  <si>
-    <t>TRANSFER LAMINA HOL LASER NERO</t>
-  </si>
-  <si>
-    <t>TRANSFER LAMINA LASER ORO NEW</t>
-  </si>
-  <si>
-    <t>TRANSFER UNITRANS 396 TR</t>
-  </si>
-  <si>
-    <t>FOLHAS PARA MARCAR A FERRO EM BOBINAS MX50 135F - OURO LADY</t>
-  </si>
-  <si>
-    <t>UNITRANS SERPENTE</t>
-  </si>
-  <si>
-    <t>TRANSFER UNITRANS 185 - PALAGI</t>
-  </si>
-  <si>
-    <t>TRANSFER UNITRANS 489 - PALAGI</t>
-  </si>
-  <si>
-    <t>TRANSFER UNITRANS 115 - PALAGI</t>
-  </si>
-  <si>
-    <t>QT-200A FULL TRANSFER - CAFÉ</t>
-  </si>
-  <si>
-    <t>QT-077A FULL TRANSFER - WHISKY</t>
-  </si>
-  <si>
     <t>QT</t>
   </si>
   <si>
+    <t>CARTEGE</t>
+  </si>
+  <si>
+    <t>UNITRANS</t>
+  </si>
+  <si>
+    <t>ECOTEX</t>
+  </si>
+  <si>
     <t>FURTACOR</t>
   </si>
   <si>
+    <t>PARCIAL IMPORTADO</t>
+  </si>
+  <si>
     <t>PARCIAL NACIONAL</t>
   </si>
   <si>
-    <t>CARTEGE</t>
-  </si>
-  <si>
     <t>TOTAL IMPORTADO</t>
   </si>
   <si>
-    <t>PARCIAL IMPORTADO</t>
-  </si>
-  <si>
-    <t>ECOTEX</t>
-  </si>
-  <si>
-    <t>UNITRANS</t>
-  </si>
-  <si>
     <t>TOTAL NACIONAL</t>
   </si>
   <si>
     <t>STARTLIGHT</t>
+  </si>
+  <si>
+    <t>HOT STAMP FULL HOLOGRAFICO CELAR CONFETE</t>
   </si>
 </sst>
 </file>
@@ -444,7 +438,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[Blue]###########0;[Red]\-###########0"/>
-    <numFmt numFmtId="166" formatCode="[Blue]###,###,###,##0.000;[Red]\-###,###,###,##0.000"/>
+    <numFmt numFmtId="165" formatCode="[Blue]###,###,###,##0.000;[Red]\-###,###,###,##0.000"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -474,7 +468,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -497,18 +491,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -853,24 +857,24 @@
     <col min="2" max="2" width="62.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.5546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>4</v>
+      <c r="D1" s="5" t="s">
+        <v>118</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>5</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -878,15 +882,15 @@
         <v>27</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C2" s="4">
-        <v>829.5</v>
+        <v>529.5</v>
       </c>
       <c r="D2" s="3">
         <v>12</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" t="s">
         <v>124</v>
       </c>
     </row>
@@ -895,7 +899,7 @@
         <v>192</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C3" s="4">
         <v>495</v>
@@ -903,8 +907,8 @@
       <c r="D3" s="3">
         <v>12</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>125</v>
+      <c r="E3" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -912,7 +916,7 @@
         <v>193</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C4" s="4">
         <v>2917</v>
@@ -920,8 +924,8 @@
       <c r="D4" s="3">
         <v>12</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>125</v>
+      <c r="E4" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -929,7 +933,7 @@
         <v>194</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C5" s="4">
         <v>995</v>
@@ -937,8 +941,8 @@
       <c r="D5" s="3">
         <v>12</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>125</v>
+      <c r="E5" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -946,7 +950,7 @@
         <v>195</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C6" s="4">
         <v>500</v>
@@ -954,8 +958,8 @@
       <c r="D6" s="3">
         <v>12</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>125</v>
+      <c r="E6" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -963,7 +967,7 @@
         <v>204</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C7" s="4">
         <v>2646</v>
@@ -971,8 +975,8 @@
       <c r="D7" s="3">
         <v>12</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>125</v>
+      <c r="E7" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -980,7 +984,7 @@
         <v>381</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C8" s="4">
         <v>4899.5</v>
@@ -988,8 +992,8 @@
       <c r="D8" s="3">
         <v>12</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>125</v>
+      <c r="E8" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -997,7 +1001,7 @@
         <v>383</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C9" s="4">
         <v>200</v>
@@ -1005,8 +1009,8 @@
       <c r="D9" s="3">
         <v>12</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>126</v>
+      <c r="E9" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -1014,7 +1018,7 @@
         <v>399</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C10" s="4">
         <v>200</v>
@@ -1022,8 +1026,8 @@
       <c r="D10" s="3">
         <v>12</v>
       </c>
-      <c r="E10" s="6" t="s">
-        <v>126</v>
+      <c r="E10" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -1031,7 +1035,7 @@
         <v>1006</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C11" s="4">
         <v>236</v>
@@ -1039,8 +1043,8 @@
       <c r="D11" s="3">
         <v>12</v>
       </c>
-      <c r="E11" s="6" t="s">
-        <v>125</v>
+      <c r="E11" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -1048,7 +1052,7 @@
         <v>1053</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C12" s="4">
         <v>300</v>
@@ -1056,8 +1060,8 @@
       <c r="D12" s="3">
         <v>12</v>
       </c>
-      <c r="E12" s="6" t="s">
-        <v>125</v>
+      <c r="E12" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -1065,7 +1069,7 @@
         <v>2890</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C13" s="4">
         <v>600</v>
@@ -1073,8 +1077,8 @@
       <c r="D13" s="3">
         <v>12</v>
       </c>
-      <c r="E13" s="6" t="s">
-        <v>125</v>
+      <c r="E13" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -1082,7 +1086,7 @@
         <v>2891</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C14" s="4">
         <v>1489</v>
@@ -1090,8 +1094,8 @@
       <c r="D14" s="3">
         <v>12</v>
       </c>
-      <c r="E14" s="6" t="s">
-        <v>125</v>
+      <c r="E14" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -1099,7 +1103,7 @@
         <v>2905</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C15" s="4">
         <v>84</v>
@@ -1107,8 +1111,8 @@
       <c r="D15" s="3">
         <v>12</v>
       </c>
-      <c r="E15" s="6" t="s">
-        <v>125</v>
+      <c r="E15" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -1116,7 +1120,7 @@
         <v>3044</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C16" s="4">
         <v>544</v>
@@ -1124,8 +1128,8 @@
       <c r="D16" s="3">
         <v>12</v>
       </c>
-      <c r="E16" s="6" t="s">
-        <v>125</v>
+      <c r="E16" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -1133,7 +1137,7 @@
         <v>3109</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C17" s="4">
         <v>4832</v>
@@ -1141,8 +1145,8 @@
       <c r="D17" s="3">
         <v>12</v>
       </c>
-      <c r="E17" s="6" t="s">
-        <v>125</v>
+      <c r="E17" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -1150,7 +1154,7 @@
         <v>3211</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C18" s="4">
         <v>1950</v>
@@ -1158,8 +1162,8 @@
       <c r="D18" s="3">
         <v>12</v>
       </c>
-      <c r="E18" s="6" t="s">
-        <v>125</v>
+      <c r="E18" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -1167,7 +1171,7 @@
         <v>3495</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C19" s="4">
         <v>2199</v>
@@ -1175,8 +1179,8 @@
       <c r="D19" s="3">
         <v>12</v>
       </c>
-      <c r="E19" s="6" t="s">
-        <v>125</v>
+      <c r="E19" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -1184,7 +1188,7 @@
         <v>4010</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C20" s="4">
         <v>491</v>
@@ -1192,8 +1196,8 @@
       <c r="D20" s="3">
         <v>12</v>
       </c>
-      <c r="E20" s="6" t="s">
-        <v>125</v>
+      <c r="E20" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -1201,7 +1205,7 @@
         <v>4067</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C21" s="4">
         <v>40</v>
@@ -1209,8 +1213,8 @@
       <c r="D21" s="3">
         <v>12</v>
       </c>
-      <c r="E21" s="6" t="s">
-        <v>125</v>
+      <c r="E21" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -1218,7 +1222,7 @@
         <v>4375</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C22" s="4">
         <v>900</v>
@@ -1226,8 +1230,8 @@
       <c r="D22" s="3">
         <v>12</v>
       </c>
-      <c r="E22" s="6" t="s">
-        <v>125</v>
+      <c r="E22" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -1235,7 +1239,7 @@
         <v>4376</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C23" s="4">
         <v>2819</v>
@@ -1243,8 +1247,8 @@
       <c r="D23" s="3">
         <v>12</v>
       </c>
-      <c r="E23" s="6" t="s">
-        <v>125</v>
+      <c r="E23" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -1252,7 +1256,7 @@
         <v>4423</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C24" s="4">
         <v>100</v>
@@ -1260,8 +1264,8 @@
       <c r="D24" s="3">
         <v>12</v>
       </c>
-      <c r="E24" s="6" t="s">
-        <v>125</v>
+      <c r="E24" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -1269,7 +1273,7 @@
         <v>4721</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C25" s="4">
         <v>1701.5</v>
@@ -1277,7 +1281,7 @@
       <c r="D25" s="3">
         <v>12</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="E25" t="s">
         <v>127</v>
       </c>
     </row>
@@ -1286,16 +1290,16 @@
         <v>4722</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C26" s="4">
-        <v>4083.5</v>
+        <v>3883.5</v>
       </c>
       <c r="D26" s="3">
         <v>12</v>
       </c>
-      <c r="E26" s="6" t="s">
-        <v>128</v>
+      <c r="E26" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -1303,7 +1307,7 @@
         <v>4723</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C27" s="4">
         <v>2974.5</v>
@@ -1311,8 +1315,8 @@
       <c r="D27" s="3">
         <v>12</v>
       </c>
-      <c r="E27" s="6" t="s">
-        <v>128</v>
+      <c r="E27" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -1320,7 +1324,7 @@
         <v>5024</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C28" s="4">
         <v>3325.5</v>
@@ -1328,8 +1332,8 @@
       <c r="D28" s="3">
         <v>12</v>
       </c>
-      <c r="E28" s="6" t="s">
-        <v>128</v>
+      <c r="E28" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
@@ -1337,7 +1341,7 @@
         <v>5025</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C29" s="4">
         <v>3064.5</v>
@@ -1345,8 +1349,8 @@
       <c r="D29" s="3">
         <v>12</v>
       </c>
-      <c r="E29" s="6" t="s">
-        <v>128</v>
+      <c r="E29" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -1354,7 +1358,7 @@
         <v>5437</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C30" s="4">
         <v>70</v>
@@ -1362,8 +1366,8 @@
       <c r="D30" s="3">
         <v>12</v>
       </c>
-      <c r="E30" s="6" t="s">
-        <v>125</v>
+      <c r="E30" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
@@ -1371,7 +1375,7 @@
         <v>5861</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C31" s="4">
         <v>328</v>
@@ -1379,8 +1383,8 @@
       <c r="D31" s="3">
         <v>12</v>
       </c>
-      <c r="E31" s="6" t="s">
-        <v>129</v>
+      <c r="E31" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
@@ -1388,7 +1392,7 @@
         <v>5931</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C32" s="4">
         <v>11</v>
@@ -1396,8 +1400,8 @@
       <c r="D32" s="3">
         <v>12</v>
       </c>
-      <c r="E32" s="6" t="s">
-        <v>125</v>
+      <c r="E32" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
@@ -1405,7 +1409,7 @@
         <v>5932</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C33" s="4">
         <v>80</v>
@@ -1413,8 +1417,8 @@
       <c r="D33" s="3">
         <v>12</v>
       </c>
-      <c r="E33" s="6" t="s">
-        <v>125</v>
+      <c r="E33" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
@@ -1422,7 +1426,7 @@
         <v>6248</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C34" s="4">
         <v>350</v>
@@ -1430,8 +1434,8 @@
       <c r="D34" s="3">
         <v>12</v>
       </c>
-      <c r="E34" s="6" t="s">
-        <v>125</v>
+      <c r="E34" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
@@ -1439,7 +1443,7 @@
         <v>6560</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C35" s="4">
         <v>2083.5</v>
@@ -1447,8 +1451,8 @@
       <c r="D35" s="3">
         <v>12</v>
       </c>
-      <c r="E35" s="6" t="s">
-        <v>128</v>
+      <c r="E35" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
@@ -1456,7 +1460,7 @@
         <v>7425</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C36" s="4">
         <v>300</v>
@@ -1464,8 +1468,8 @@
       <c r="D36" s="3">
         <v>12</v>
       </c>
-      <c r="E36" s="6" t="s">
-        <v>123</v>
+      <c r="E36" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
@@ -1473,16 +1477,16 @@
         <v>7425</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C37" s="4">
-        <v>4858.78</v>
+        <v>8188.78</v>
       </c>
       <c r="D37" s="3">
         <v>12</v>
       </c>
-      <c r="E37" s="6" t="s">
-        <v>123</v>
+      <c r="E37" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
@@ -1490,16 +1494,16 @@
         <v>7484</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C38" s="4">
-        <v>2850</v>
+        <v>10470</v>
       </c>
       <c r="D38" s="3">
         <v>12</v>
       </c>
-      <c r="E38" s="6" t="s">
-        <v>123</v>
+      <c r="E38" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
@@ -1507,16 +1511,16 @@
         <v>7485</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C39" s="4">
-        <v>2804.5</v>
+        <v>6804.5</v>
       </c>
       <c r="D39" s="3">
         <v>12</v>
       </c>
-      <c r="E39" s="6" t="s">
-        <v>123</v>
+      <c r="E39" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -1524,16 +1528,16 @@
         <v>7486</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C40" s="4">
-        <v>19080.5</v>
+        <v>18480.5</v>
       </c>
       <c r="D40" s="3">
         <v>12</v>
       </c>
-      <c r="E40" s="6" t="s">
-        <v>123</v>
+      <c r="E40" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
@@ -1541,7 +1545,7 @@
         <v>7771</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C41" s="4">
         <v>1191</v>
@@ -1549,8 +1553,8 @@
       <c r="D41" s="3">
         <v>12</v>
       </c>
-      <c r="E41" s="6" t="s">
-        <v>130</v>
+      <c r="E41" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
@@ -1558,7 +1562,7 @@
         <v>8111</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C42" s="4">
         <v>383</v>
@@ -1566,8 +1570,8 @@
       <c r="D42" s="3">
         <v>12</v>
       </c>
-      <c r="E42" s="6" t="s">
-        <v>128</v>
+      <c r="E42" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
@@ -1575,7 +1579,7 @@
         <v>8175</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C43" s="4">
         <v>2377.5</v>
@@ -1583,8 +1587,8 @@
       <c r="D43" s="3">
         <v>12</v>
       </c>
-      <c r="E43" s="6" t="s">
-        <v>123</v>
+      <c r="E43" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
@@ -1592,7 +1596,7 @@
         <v>8418</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C44" s="4">
         <v>954.5</v>
@@ -1600,8 +1604,8 @@
       <c r="D44" s="3">
         <v>12</v>
       </c>
-      <c r="E44" s="6" t="s">
-        <v>123</v>
+      <c r="E44" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
@@ -1609,7 +1613,7 @@
         <v>8472</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C45" s="4">
         <v>10</v>
@@ -1617,8 +1621,8 @@
       <c r="D45" s="3">
         <v>12</v>
       </c>
-      <c r="E45" s="6" t="s">
-        <v>131</v>
+      <c r="E45" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
@@ -1626,7 +1630,7 @@
         <v>8612</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C46" s="4">
         <v>600</v>
@@ -1634,8 +1638,8 @@
       <c r="D46" s="3">
         <v>12</v>
       </c>
-      <c r="E46" s="6" t="s">
-        <v>125</v>
+      <c r="E46" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
@@ -1643,7 +1647,7 @@
         <v>8613</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C47" s="4">
         <v>410</v>
@@ -1651,8 +1655,8 @@
       <c r="D47" s="3">
         <v>12</v>
       </c>
-      <c r="E47" s="6" t="s">
-        <v>125</v>
+      <c r="E47" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
@@ -1660,7 +1664,7 @@
         <v>8645</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C48" s="4">
         <v>35</v>
@@ -1668,8 +1672,8 @@
       <c r="D48" s="3">
         <v>12</v>
       </c>
-      <c r="E48" s="6" t="s">
-        <v>125</v>
+      <c r="E48" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
@@ -1677,7 +1681,7 @@
         <v>8713</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C49" s="4">
         <v>463</v>
@@ -1685,8 +1689,8 @@
       <c r="D49" s="3">
         <v>12</v>
       </c>
-      <c r="E49" s="6" t="s">
-        <v>130</v>
+      <c r="E49" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
@@ -1694,7 +1698,7 @@
         <v>9000</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C50" s="4">
         <v>798.5</v>
@@ -1702,8 +1706,8 @@
       <c r="D50" s="3">
         <v>12</v>
       </c>
-      <c r="E50" s="6" t="s">
-        <v>123</v>
+      <c r="E50" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
@@ -1711,7 +1715,7 @@
         <v>9009</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C51" s="4">
         <v>60</v>
@@ -1719,8 +1723,8 @@
       <c r="D51" s="3">
         <v>12</v>
       </c>
-      <c r="E51" s="6" t="s">
-        <v>129</v>
+      <c r="E51" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
@@ -1728,7 +1732,7 @@
         <v>9336</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C52" s="4">
         <v>1318.5</v>
@@ -1736,8 +1740,8 @@
       <c r="D52" s="3">
         <v>12</v>
       </c>
-      <c r="E52" s="6" t="s">
-        <v>130</v>
+      <c r="E52" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
@@ -1745,7 +1749,7 @@
         <v>9396</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C53" s="4">
         <v>435.5</v>
@@ -1753,8 +1757,8 @@
       <c r="D53" s="3">
         <v>12</v>
       </c>
-      <c r="E53" s="6" t="s">
-        <v>132</v>
+      <c r="E53" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
@@ -1762,7 +1766,7 @@
         <v>9397</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C54" s="4">
         <v>1499</v>
@@ -1770,8 +1774,8 @@
       <c r="D54" s="3">
         <v>12</v>
       </c>
-      <c r="E54" s="6" t="s">
-        <v>132</v>
+      <c r="E54" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
@@ -1779,7 +1783,7 @@
         <v>9398</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C55" s="4">
         <v>1199</v>
@@ -1787,8 +1791,8 @@
       <c r="D55" s="3">
         <v>12</v>
       </c>
-      <c r="E55" s="6" t="s">
-        <v>132</v>
+      <c r="E55" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
@@ -1796,7 +1800,7 @@
         <v>9399</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C56" s="4">
         <v>594</v>
@@ -1804,8 +1808,8 @@
       <c r="D56" s="3">
         <v>12</v>
       </c>
-      <c r="E56" s="6" t="s">
-        <v>132</v>
+      <c r="E56" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
@@ -1813,7 +1817,7 @@
         <v>9430</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C57" s="4">
         <v>25</v>
@@ -1821,8 +1825,8 @@
       <c r="D57" s="3">
         <v>12</v>
       </c>
-      <c r="E57" s="6" t="s">
-        <v>125</v>
+      <c r="E57" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
@@ -1830,7 +1834,7 @@
         <v>9430</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C58" s="4">
         <v>2327.8000000000002</v>
@@ -1838,8 +1842,8 @@
       <c r="D58" s="3">
         <v>12</v>
       </c>
-      <c r="E58" s="6" t="s">
-        <v>125</v>
+      <c r="E58" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
@@ -1847,7 +1851,7 @@
         <v>9476</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C59" s="4">
         <v>1768.5</v>
@@ -1855,8 +1859,8 @@
       <c r="D59" s="3">
         <v>12</v>
       </c>
-      <c r="E59" s="6" t="s">
-        <v>125</v>
+      <c r="E59" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
@@ -1864,7 +1868,7 @@
         <v>9591</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C60" s="4">
         <v>5</v>
@@ -1872,8 +1876,8 @@
       <c r="D60" s="3">
         <v>12</v>
       </c>
-      <c r="E60" s="6" t="s">
-        <v>125</v>
+      <c r="E60" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
@@ -1881,7 +1885,7 @@
         <v>9633</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C61" s="4">
         <v>400</v>
@@ -1889,8 +1893,8 @@
       <c r="D61" s="3">
         <v>12</v>
       </c>
-      <c r="E61" s="6" t="s">
-        <v>125</v>
+      <c r="E61" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
@@ -1898,7 +1902,7 @@
         <v>9804</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C62" s="4">
         <v>1058</v>
@@ -1906,8 +1910,8 @@
       <c r="D62" s="3">
         <v>12</v>
       </c>
-      <c r="E62" s="6" t="s">
-        <v>123</v>
+      <c r="E62" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
@@ -1915,7 +1919,7 @@
         <v>9805</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C63" s="4">
         <v>40</v>
@@ -1923,8 +1927,8 @@
       <c r="D63" s="3">
         <v>12</v>
       </c>
-      <c r="E63" s="6" t="s">
-        <v>125</v>
+      <c r="E63" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
@@ -1932,7 +1936,7 @@
         <v>10026</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C64" s="4">
         <v>5</v>
@@ -1940,8 +1944,8 @@
       <c r="D64" s="3">
         <v>12</v>
       </c>
-      <c r="E64" s="6" t="s">
-        <v>125</v>
+      <c r="E64" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
@@ -1949,7 +1953,7 @@
         <v>10027</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C65" s="4">
         <v>5</v>
@@ -1957,8 +1961,8 @@
       <c r="D65" s="3">
         <v>12</v>
       </c>
-      <c r="E65" s="6" t="s">
-        <v>125</v>
+      <c r="E65" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
@@ -1966,7 +1970,7 @@
         <v>10028</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C66" s="4">
         <v>8</v>
@@ -1974,8 +1978,8 @@
       <c r="D66" s="3">
         <v>12</v>
       </c>
-      <c r="E66" s="6" t="s">
-        <v>125</v>
+      <c r="E66" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
@@ -1983,7 +1987,7 @@
         <v>10031</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C67" s="4">
         <v>15</v>
@@ -1991,8 +1995,8 @@
       <c r="D67" s="3">
         <v>12</v>
       </c>
-      <c r="E67" s="6" t="s">
-        <v>125</v>
+      <c r="E67" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
@@ -2000,7 +2004,7 @@
         <v>10042</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C68" s="4">
         <v>100</v>
@@ -2008,8 +2012,8 @@
       <c r="D68" s="3">
         <v>12</v>
       </c>
-      <c r="E68" s="6" t="s">
-        <v>125</v>
+      <c r="E68" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
@@ -2017,7 +2021,7 @@
         <v>10042</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C69" s="4">
         <v>945</v>
@@ -2025,8 +2029,8 @@
       <c r="D69" s="3">
         <v>12</v>
       </c>
-      <c r="E69" s="6" t="s">
-        <v>125</v>
+      <c r="E69" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
@@ -2034,7 +2038,7 @@
         <v>10044</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C70" s="4">
         <v>80</v>
@@ -2042,8 +2046,8 @@
       <c r="D70" s="3">
         <v>12</v>
       </c>
-      <c r="E70" s="6" t="s">
-        <v>125</v>
+      <c r="E70" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
@@ -2051,7 +2055,7 @@
         <v>10080</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C71" s="4">
         <v>50</v>
@@ -2059,84 +2063,84 @@
       <c r="D71" s="3">
         <v>12</v>
       </c>
-      <c r="E71" s="6" t="s">
-        <v>123</v>
+      <c r="E71" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="3">
-        <v>10090</v>
+        <v>10254</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C72" s="4">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="D72" s="3">
         <v>12</v>
       </c>
-      <c r="E72" s="6" t="s">
-        <v>123</v>
+      <c r="E72" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="3">
-        <v>10254</v>
+        <v>10318</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C73" s="4">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="D73" s="3">
         <v>12</v>
       </c>
-      <c r="E73" s="6" t="s">
-        <v>125</v>
+      <c r="E73" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="3">
-        <v>10318</v>
+        <v>10362</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C74" s="4">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D74" s="3">
         <v>12</v>
       </c>
-      <c r="E74" s="6" t="s">
-        <v>125</v>
+      <c r="E74" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="3">
-        <v>10362</v>
+        <v>10692</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C75" s="4">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D75" s="3">
         <v>12</v>
       </c>
-      <c r="E75" s="6" t="s">
-        <v>125</v>
+      <c r="E75" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="3">
-        <v>10692</v>
+        <v>10707</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C76" s="4">
         <v>3</v>
@@ -2144,16 +2148,16 @@
       <c r="D76" s="3">
         <v>12</v>
       </c>
-      <c r="E76" s="6" t="s">
-        <v>130</v>
+      <c r="E76" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="3">
-        <v>10707</v>
+        <v>10725</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C77" s="4">
         <v>3</v>
@@ -2161,84 +2165,84 @@
       <c r="D77" s="3">
         <v>12</v>
       </c>
-      <c r="E77" s="6" t="s">
-        <v>125</v>
+      <c r="E77" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="3">
-        <v>10725</v>
+        <v>10762</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C78" s="4">
-        <v>3</v>
+        <v>1376.8</v>
       </c>
       <c r="D78" s="3">
         <v>12</v>
       </c>
-      <c r="E78" s="6" t="s">
-        <v>130</v>
+      <c r="E78" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="3">
-        <v>10762</v>
+        <v>10830</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C79" s="4">
-        <v>1376.8</v>
+        <v>3</v>
       </c>
       <c r="D79" s="3">
         <v>12</v>
       </c>
-      <c r="E79" s="6" t="s">
-        <v>130</v>
+      <c r="E79" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="3">
-        <v>10830</v>
+        <v>10832</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C80" s="4">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D80" s="3">
         <v>12</v>
       </c>
-      <c r="E80" s="6" t="s">
-        <v>130</v>
+      <c r="E80" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="3">
-        <v>10832</v>
+        <v>10834</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C81" s="4">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D81" s="3">
         <v>12</v>
       </c>
-      <c r="E81" s="6" t="s">
-        <v>125</v>
+      <c r="E81" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="3">
-        <v>10834</v>
+        <v>10836</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="C82" s="4">
         <v>5</v>
@@ -2246,101 +2250,101 @@
       <c r="D82" s="3">
         <v>12</v>
       </c>
-      <c r="E82" s="6" t="s">
-        <v>125</v>
+      <c r="E82" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="3">
-        <v>10836</v>
+        <v>10936</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="C83" s="4">
-        <v>5</v>
+        <v>1093.3499999999999</v>
       </c>
       <c r="D83" s="3">
         <v>12</v>
       </c>
-      <c r="E83" s="6" t="s">
-        <v>125</v>
+      <c r="E83" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="3">
-        <v>10936</v>
+        <v>10937</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C84" s="4">
-        <v>1093.3499999999999</v>
+        <v>1183.5</v>
       </c>
       <c r="D84" s="3">
         <v>12</v>
       </c>
-      <c r="E84" s="6" t="s">
-        <v>123</v>
+      <c r="E84" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="3">
-        <v>10937</v>
+        <v>10997</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C85" s="4">
-        <v>1183.5</v>
+        <v>188.5</v>
       </c>
       <c r="D85" s="3">
         <v>12</v>
       </c>
-      <c r="E85" s="6" t="s">
-        <v>123</v>
+      <c r="E85" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="3">
-        <v>10997</v>
+        <v>10998</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C86" s="4">
-        <v>188.5</v>
+        <v>790.35299999999995</v>
       </c>
       <c r="D86" s="3">
         <v>12</v>
       </c>
-      <c r="E86" s="6" t="s">
-        <v>125</v>
+      <c r="E86" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="3">
-        <v>10998</v>
+        <v>11003</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C87" s="4">
-        <v>790.35299999999995</v>
+        <v>5</v>
       </c>
       <c r="D87" s="3">
         <v>12</v>
       </c>
-      <c r="E87" s="6" t="s">
-        <v>125</v>
+      <c r="E87" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="3">
-        <v>11003</v>
+        <v>11105</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C88" s="4">
         <v>5</v>
@@ -2348,84 +2352,84 @@
       <c r="D88" s="3">
         <v>12</v>
       </c>
-      <c r="E88" s="6" t="s">
-        <v>125</v>
+      <c r="E88" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="3">
-        <v>11105</v>
+        <v>11106</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C89" s="4">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D89" s="3">
         <v>12</v>
       </c>
-      <c r="E89" s="6" t="s">
-        <v>125</v>
+      <c r="E89" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="3">
-        <v>11106</v>
+        <v>11107</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C90" s="4">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D90" s="3">
         <v>12</v>
       </c>
-      <c r="E90" s="6" t="s">
-        <v>125</v>
+      <c r="E90" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="3">
-        <v>11107</v>
+        <v>11243</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C91" s="4">
-        <v>5</v>
+        <v>209</v>
       </c>
       <c r="D91" s="3">
         <v>12</v>
       </c>
-      <c r="E91" s="6" t="s">
-        <v>125</v>
+      <c r="E91" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="3">
-        <v>11243</v>
+        <v>11269</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C92" s="4">
-        <v>209</v>
+        <v>10</v>
       </c>
       <c r="D92" s="3">
         <v>12</v>
       </c>
-      <c r="E92" s="6" t="s">
-        <v>125</v>
+      <c r="E92" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="3">
-        <v>11269</v>
+        <v>11316</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C93" s="4">
         <v>10</v>
@@ -2433,118 +2437,118 @@
       <c r="D93" s="3">
         <v>12</v>
       </c>
-      <c r="E93" s="6" t="s">
-        <v>125</v>
+      <c r="E93" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="3">
-        <v>11316</v>
+        <v>11318</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C94" s="4">
-        <v>10</v>
+        <v>97.7</v>
       </c>
       <c r="D94" s="3">
         <v>12</v>
       </c>
-      <c r="E94" s="6" t="s">
-        <v>125</v>
+      <c r="E94" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="3">
-        <v>11318</v>
+        <v>11362</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C95" s="4">
-        <v>97.7</v>
+        <v>5</v>
       </c>
       <c r="D95" s="3">
         <v>12</v>
       </c>
-      <c r="E95" s="6" t="s">
-        <v>125</v>
+      <c r="E95" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="3">
-        <v>11362</v>
+        <v>11396</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C96" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D96" s="3">
         <v>12</v>
       </c>
-      <c r="E96" s="6" t="s">
-        <v>125</v>
+      <c r="E96" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="3">
-        <v>11396</v>
+        <v>11397</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C97" s="4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D97" s="3">
         <v>12</v>
       </c>
-      <c r="E97" s="6" t="s">
-        <v>125</v>
+      <c r="E97" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="3">
-        <v>11397</v>
+        <v>11444</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C98" s="4">
-        <v>5</v>
+        <v>230</v>
       </c>
       <c r="D98" s="3">
         <v>12</v>
       </c>
-      <c r="E98" s="6" t="s">
-        <v>125</v>
+      <c r="E98" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="3">
-        <v>11444</v>
+        <v>12497</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C99" s="4">
-        <v>230</v>
+        <v>5</v>
       </c>
       <c r="D99" s="3">
         <v>12</v>
       </c>
-      <c r="E99" s="6" t="s">
-        <v>125</v>
+      <c r="E99" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="3">
-        <v>12497</v>
+        <v>12498</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C100" s="4">
         <v>5</v>
@@ -2552,16 +2556,16 @@
       <c r="D100" s="3">
         <v>12</v>
       </c>
-      <c r="E100" s="6" t="s">
-        <v>130</v>
+      <c r="E100" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" s="3">
-        <v>12498</v>
+        <v>12499</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C101" s="4">
         <v>5</v>
@@ -2569,16 +2573,16 @@
       <c r="D101" s="3">
         <v>12</v>
       </c>
-      <c r="E101" s="6" t="s">
-        <v>125</v>
+      <c r="E101" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="3">
-        <v>12499</v>
+        <v>12501</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C102" s="4">
         <v>5</v>
@@ -2586,16 +2590,16 @@
       <c r="D102" s="3">
         <v>12</v>
       </c>
-      <c r="E102" s="6" t="s">
-        <v>125</v>
+      <c r="E102" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="3">
-        <v>12501</v>
+        <v>12503</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C103" s="4">
         <v>5</v>
@@ -2603,16 +2607,16 @@
       <c r="D103" s="3">
         <v>12</v>
       </c>
-      <c r="E103" s="6" t="s">
-        <v>125</v>
+      <c r="E103" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" s="3">
-        <v>12503</v>
+        <v>12504</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C104" s="4">
         <v>5</v>
@@ -2620,152 +2624,152 @@
       <c r="D104" s="3">
         <v>12</v>
       </c>
-      <c r="E104" s="6" t="s">
-        <v>130</v>
+      <c r="E104" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" s="3">
-        <v>12504</v>
+        <v>12514</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C105" s="4">
-        <v>5</v>
+        <v>2329.1</v>
       </c>
       <c r="D105" s="3">
         <v>12</v>
       </c>
-      <c r="E105" s="6" t="s">
+      <c r="E105" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" s="3">
-        <v>12514</v>
+        <v>12516</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C106" s="4">
-        <v>2329.1</v>
+        <v>2474.6</v>
       </c>
       <c r="D106" s="3">
         <v>12</v>
       </c>
-      <c r="E106" s="6" t="s">
-        <v>128</v>
+      <c r="E106" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" s="3">
-        <v>12515</v>
+        <v>12517</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C107" s="4">
-        <v>556.41</v>
+        <v>1553.1</v>
       </c>
       <c r="D107" s="3">
         <v>12</v>
       </c>
-      <c r="E107" s="6" t="s">
-        <v>128</v>
+      <c r="E107" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="3">
-        <v>12516</v>
+        <v>12518</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C108" s="4">
-        <v>2474.6</v>
+        <v>1378.5</v>
       </c>
       <c r="D108" s="3">
         <v>12</v>
       </c>
-      <c r="E108" s="6" t="s">
-        <v>128</v>
+      <c r="E108" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" s="3">
-        <v>12517</v>
+        <v>12673</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C109" s="4">
-        <v>1553.1</v>
+        <v>5</v>
       </c>
       <c r="D109" s="3">
         <v>12</v>
       </c>
-      <c r="E109" s="6" t="s">
-        <v>128</v>
+      <c r="E109" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" s="3">
-        <v>12518</v>
+        <v>13150</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C110" s="4">
-        <v>1578.5</v>
+        <v>637.20000000000005</v>
       </c>
       <c r="D110" s="3">
         <v>12</v>
       </c>
-      <c r="E110" s="6" t="s">
-        <v>128</v>
+      <c r="E110" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" s="3">
-        <v>12673</v>
+        <v>14365</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C111" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D111" s="3">
         <v>12</v>
       </c>
-      <c r="E111" s="6" t="s">
-        <v>125</v>
+      <c r="E111" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="3">
-        <v>13150</v>
+        <v>14366</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C112" s="4">
-        <v>637.20000000000005</v>
+        <v>2</v>
       </c>
       <c r="D112" s="3">
         <v>12</v>
       </c>
-      <c r="E112" s="6" t="s">
-        <v>128</v>
+      <c r="E112" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" s="3">
-        <v>14365</v>
+        <v>14367</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C113" s="4">
         <v>2</v>
@@ -2773,84 +2777,84 @@
       <c r="D113" s="3">
         <v>12</v>
       </c>
-      <c r="E113" s="6" t="s">
-        <v>125</v>
+      <c r="E113" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="3">
-        <v>14366</v>
+        <v>14928</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C114" s="4">
-        <v>2</v>
+        <v>7.5</v>
       </c>
       <c r="D114" s="3">
         <v>12</v>
       </c>
-      <c r="E114" s="6" t="s">
-        <v>125</v>
+      <c r="E114" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="3">
-        <v>14367</v>
+        <v>15405</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C115" s="4">
-        <v>2</v>
+        <v>225</v>
       </c>
       <c r="D115" s="3">
         <v>12</v>
       </c>
-      <c r="E115" s="6" t="s">
-        <v>130</v>
+      <c r="E115" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" s="3">
-        <v>14928</v>
+        <v>16460</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C116" s="4">
-        <v>7.5</v>
+        <v>1</v>
       </c>
       <c r="D116" s="3">
         <v>12</v>
       </c>
-      <c r="E116" s="6" t="s">
-        <v>125</v>
+      <c r="E116" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" s="3">
-        <v>15405</v>
+        <v>16461</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C117" s="4">
-        <v>225</v>
+        <v>1</v>
       </c>
       <c r="D117" s="3">
         <v>12</v>
       </c>
-      <c r="E117" s="6" t="s">
-        <v>130</v>
+      <c r="E117" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" s="3">
-        <v>16460</v>
+        <v>16462</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C118" s="4">
         <v>1</v>
@@ -2858,77 +2862,65 @@
       <c r="D118" s="3">
         <v>12</v>
       </c>
-      <c r="E118" s="6" t="s">
-        <v>130</v>
+      <c r="E118" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" s="3">
-        <v>16461</v>
+        <v>17075</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C119" s="4">
-        <v>1</v>
+        <v>1832</v>
       </c>
       <c r="D119" s="3">
         <v>12</v>
       </c>
-      <c r="E119" s="6" t="s">
-        <v>130</v>
+      <c r="E119" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" s="3">
-        <v>16462</v>
+        <v>17076</v>
       </c>
       <c r="B120" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C120" s="4">
+        <v>1141.8</v>
+      </c>
+      <c r="D120" s="3">
+        <v>12</v>
+      </c>
+      <c r="E120" t="s">
         <v>120</v>
-      </c>
-      <c r="C120" s="4">
-        <v>1</v>
-      </c>
-      <c r="D120" s="3">
-        <v>12</v>
-      </c>
-      <c r="E120" s="6" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" s="3">
-        <v>17075</v>
+        <v>17863</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="C121" s="4">
-        <v>3712</v>
+        <v>500</v>
       </c>
       <c r="D121" s="3">
         <v>12</v>
       </c>
-      <c r="E121" s="6" t="s">
-        <v>123</v>
+      <c r="E121" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A122" s="3">
-        <v>17076</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C122" s="4">
-        <v>1141.8</v>
-      </c>
-      <c r="D122" s="3">
-        <v>12</v>
-      </c>
-      <c r="E122" s="6" t="s">
-        <v>123</v>
-      </c>
+      <c r="A122" s="3"/>
+      <c r="B122" s="1"/>
+      <c r="C122" s="4"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E122" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/data-source/ESTOQUETRANSFER.xlsx
+++ b/data-source/ESTOQUETRANSFER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/TRANSFER-ANALISE/data-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{20405EE4-7847-4583-ADA9-6FB66CEB9340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B23CEC38-E292-4C09-AB0F-363D0F097CA9}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="8_{20405EE4-7847-4583-ADA9-6FB66CEB9340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ECC96B09-B354-4EDD-ABF2-EAC7B159E980}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="132">
   <si>
     <t>Produto</t>
   </si>
@@ -429,7 +429,10 @@
     <t>STARTLIGHT</t>
   </si>
   <si>
-    <t>HOT STAMP FULL HOLOGRAFICO CELAR CONFETE</t>
+    <t>DOTS FILM LASER - AMERICA ASIA</t>
+  </si>
+  <si>
+    <t>PONTILHADO</t>
   </si>
 </sst>
 </file>
@@ -853,10 +856,10 @@
   <dimension ref="A1:E122"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="62.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.21875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1253,64 +1256,64 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
-        <v>4423</v>
+        <v>4413</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>25</v>
+        <v>130</v>
       </c>
       <c r="C24" s="4">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="D24" s="3">
         <v>12</v>
       </c>
       <c r="E24" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
-        <v>4721</v>
+        <v>4423</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C25" s="4">
-        <v>1701.5</v>
+        <v>100</v>
       </c>
       <c r="D25" s="3">
         <v>12</v>
       </c>
       <c r="E25" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
-        <v>4722</v>
+        <v>4721</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C26" s="4">
-        <v>3883.5</v>
+        <v>1701.5</v>
       </c>
       <c r="D26" s="3">
         <v>12</v>
       </c>
       <c r="E26" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
-        <v>4723</v>
+        <v>4722</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C27" s="4">
-        <v>2974.5</v>
+        <v>3883.5</v>
       </c>
       <c r="D27" s="3">
         <v>12</v>
@@ -1321,13 +1324,13 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
-        <v>5024</v>
+        <v>4723</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C28" s="4">
-        <v>3325.5</v>
+        <v>2974.5</v>
       </c>
       <c r="D28" s="3">
         <v>12</v>
@@ -1338,13 +1341,13 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
-        <v>5025</v>
+        <v>5024</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C29" s="4">
-        <v>3064.5</v>
+        <v>3325.5</v>
       </c>
       <c r="D29" s="3">
         <v>12</v>
@@ -1355,64 +1358,64 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
-        <v>5437</v>
+        <v>5025</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C30" s="4">
-        <v>70</v>
+        <v>3064.5</v>
       </c>
       <c r="D30" s="3">
         <v>12</v>
       </c>
       <c r="E30" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
-        <v>5861</v>
+        <v>5437</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C31" s="4">
-        <v>328</v>
+        <v>70</v>
       </c>
       <c r="D31" s="3">
         <v>12</v>
       </c>
       <c r="E31" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
-        <v>5931</v>
+        <v>5861</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C32" s="4">
-        <v>11</v>
+        <v>328</v>
       </c>
       <c r="D32" s="3">
         <v>12</v>
       </c>
       <c r="E32" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
-        <v>5932</v>
+        <v>5931</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C33" s="4">
-        <v>80</v>
+        <v>11</v>
       </c>
       <c r="D33" s="3">
         <v>12</v>
@@ -1423,13 +1426,13 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
-        <v>6248</v>
+        <v>5932</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C34" s="4">
-        <v>350</v>
+        <v>80</v>
       </c>
       <c r="D34" s="3">
         <v>12</v>
@@ -1440,36 +1443,36 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
-        <v>6560</v>
+        <v>6248</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C35" s="4">
-        <v>2083.5</v>
+        <v>350</v>
       </c>
       <c r="D35" s="3">
         <v>12</v>
       </c>
       <c r="E35" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
-        <v>7425</v>
+        <v>6560</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C36" s="4">
-        <v>300</v>
+        <v>2083.5</v>
       </c>
       <c r="D36" s="3">
         <v>12</v>
       </c>
       <c r="E36" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
@@ -1480,7 +1483,7 @@
         <v>37</v>
       </c>
       <c r="C37" s="4">
-        <v>8188.78</v>
+        <v>300</v>
       </c>
       <c r="D37" s="3">
         <v>12</v>
@@ -1491,13 +1494,13 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
-        <v>7484</v>
+        <v>7425</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C38" s="4">
-        <v>10470</v>
+        <v>7988.78</v>
       </c>
       <c r="D38" s="3">
         <v>12</v>
@@ -1508,13 +1511,13 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
-        <v>7485</v>
+        <v>7484</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C39" s="4">
-        <v>6804.5</v>
+        <v>4470</v>
       </c>
       <c r="D39" s="3">
         <v>12</v>
@@ -1525,13 +1528,13 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
-        <v>7486</v>
+        <v>7485</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C40" s="4">
-        <v>18480.5</v>
+        <v>5404.5</v>
       </c>
       <c r="D40" s="3">
         <v>12</v>
@@ -1542,64 +1545,64 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
-        <v>7771</v>
+        <v>7486</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C41" s="4">
-        <v>1191</v>
+        <v>17480.5</v>
       </c>
       <c r="D41" s="3">
         <v>12</v>
       </c>
       <c r="E41" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
-        <v>8111</v>
+        <v>7771</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C42" s="4">
-        <v>383</v>
+        <v>1191</v>
       </c>
       <c r="D42" s="3">
         <v>12</v>
       </c>
       <c r="E42" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
-        <v>8175</v>
+        <v>8111</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C43" s="4">
-        <v>2377.5</v>
+        <v>383</v>
       </c>
       <c r="D43" s="3">
         <v>12</v>
       </c>
       <c r="E43" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
-        <v>8418</v>
+        <v>8175</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C44" s="4">
-        <v>954.5</v>
+        <v>2377.5</v>
       </c>
       <c r="D44" s="3">
         <v>12</v>
@@ -1610,47 +1613,47 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
-        <v>8472</v>
+        <v>8418</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C45" s="4">
-        <v>10</v>
+        <v>954.5</v>
       </c>
       <c r="D45" s="3">
         <v>12</v>
       </c>
       <c r="E45" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
-        <v>8612</v>
+        <v>8472</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C46" s="4">
-        <v>600</v>
+        <v>10</v>
       </c>
       <c r="D46" s="3">
         <v>12</v>
       </c>
       <c r="E46" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
-        <v>8613</v>
+        <v>8612</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C47" s="4">
-        <v>410</v>
+        <v>600</v>
       </c>
       <c r="D47" s="3">
         <v>12</v>
@@ -1661,13 +1664,13 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
-        <v>8645</v>
+        <v>8613</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C48" s="4">
-        <v>35</v>
+        <v>410</v>
       </c>
       <c r="D48" s="3">
         <v>12</v>
@@ -1678,98 +1681,98 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
-        <v>8713</v>
+        <v>8645</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C49" s="4">
-        <v>463</v>
+        <v>35</v>
       </c>
       <c r="D49" s="3">
         <v>12</v>
       </c>
       <c r="E49" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
-        <v>9000</v>
+        <v>8713</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C50" s="4">
-        <v>798.5</v>
+        <v>463</v>
       </c>
       <c r="D50" s="3">
         <v>12</v>
       </c>
       <c r="E50" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
-        <v>9009</v>
+        <v>9000</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C51" s="4">
-        <v>60</v>
+        <v>8.5</v>
       </c>
       <c r="D51" s="3">
         <v>12</v>
       </c>
       <c r="E51" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
-        <v>9336</v>
+        <v>9009</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C52" s="4">
-        <v>1318.5</v>
+        <v>60</v>
       </c>
       <c r="D52" s="3">
         <v>12</v>
       </c>
       <c r="E52" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
-        <v>9396</v>
+        <v>9336</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C53" s="4">
-        <v>435.5</v>
+        <v>750.1</v>
       </c>
       <c r="D53" s="3">
         <v>12</v>
       </c>
       <c r="E53" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
-        <v>9397</v>
+        <v>9396</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C54" s="4">
-        <v>1499</v>
+        <v>435.5</v>
       </c>
       <c r="D54" s="3">
         <v>12</v>
@@ -1780,13 +1783,13 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
-        <v>9398</v>
+        <v>9397</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C55" s="4">
-        <v>1199</v>
+        <v>1499</v>
       </c>
       <c r="D55" s="3">
         <v>12</v>
@@ -1797,13 +1800,13 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
-        <v>9399</v>
+        <v>9398</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C56" s="4">
-        <v>594</v>
+        <v>1199</v>
       </c>
       <c r="D56" s="3">
         <v>12</v>
@@ -1814,19 +1817,19 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
-        <v>9430</v>
+        <v>9399</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C57" s="4">
-        <v>25</v>
+        <v>594</v>
       </c>
       <c r="D57" s="3">
         <v>12</v>
       </c>
       <c r="E57" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
@@ -1837,7 +1840,7 @@
         <v>57</v>
       </c>
       <c r="C58" s="4">
-        <v>2327.8000000000002</v>
+        <v>25</v>
       </c>
       <c r="D58" s="3">
         <v>12</v>
@@ -1848,13 +1851,13 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
-        <v>9476</v>
+        <v>9430</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C59" s="4">
-        <v>1768.5</v>
+        <v>2327.8000000000002</v>
       </c>
       <c r="D59" s="3">
         <v>12</v>
@@ -1865,13 +1868,13 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
-        <v>9591</v>
+        <v>9476</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C60" s="4">
-        <v>5</v>
+        <v>1768.5</v>
       </c>
       <c r="D60" s="3">
         <v>12</v>
@@ -1882,13 +1885,13 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
-        <v>9633</v>
+        <v>9591</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C61" s="4">
-        <v>400</v>
+        <v>5</v>
       </c>
       <c r="D61" s="3">
         <v>12</v>
@@ -1899,13 +1902,13 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
-        <v>9804</v>
+        <v>9633</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C62" s="4">
-        <v>1058</v>
+        <v>400</v>
       </c>
       <c r="D62" s="3">
         <v>12</v>
@@ -1916,13 +1919,13 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
-        <v>9805</v>
+        <v>9804</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C63" s="4">
-        <v>40</v>
+        <v>1058</v>
       </c>
       <c r="D63" s="3">
         <v>12</v>
@@ -1933,13 +1936,13 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
-        <v>10026</v>
+        <v>9805</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C64" s="4">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="D64" s="3">
         <v>12</v>
@@ -1950,10 +1953,10 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
-        <v>10027</v>
+        <v>10026</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C65" s="4">
         <v>5</v>
@@ -1967,13 +1970,13 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="3">
-        <v>10028</v>
+        <v>10027</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C66" s="4">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D66" s="3">
         <v>12</v>
@@ -1984,13 +1987,13 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
-        <v>10031</v>
+        <v>10028</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C67" s="4">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D67" s="3">
         <v>12</v>
@@ -2001,13 +2004,13 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
-        <v>10042</v>
+        <v>10031</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C68" s="4">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="D68" s="3">
         <v>12</v>
@@ -2024,7 +2027,7 @@
         <v>67</v>
       </c>
       <c r="C69" s="4">
-        <v>945</v>
+        <v>100</v>
       </c>
       <c r="D69" s="3">
         <v>12</v>
@@ -2035,13 +2038,13 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="3">
-        <v>10044</v>
+        <v>10042</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C70" s="4">
-        <v>80</v>
+        <v>945</v>
       </c>
       <c r="D70" s="3">
         <v>12</v>
@@ -2052,13 +2055,13 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="3">
-        <v>10080</v>
+        <v>10044</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C71" s="4">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="D71" s="3">
         <v>12</v>
@@ -2069,13 +2072,13 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="3">
-        <v>10254</v>
+        <v>10080</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C72" s="4">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="D72" s="3">
         <v>12</v>
@@ -2086,13 +2089,13 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="3">
-        <v>10318</v>
+        <v>10254</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C73" s="4">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="D73" s="3">
         <v>12</v>
@@ -2103,13 +2106,13 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="3">
-        <v>10362</v>
+        <v>10318</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C74" s="4">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D74" s="3">
         <v>12</v>
@@ -2120,27 +2123,27 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="3">
-        <v>10692</v>
+        <v>10362</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C75" s="4">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D75" s="3">
         <v>12</v>
       </c>
       <c r="E75" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="3">
-        <v>10707</v>
+        <v>10692</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C76" s="4">
         <v>3</v>
@@ -2149,15 +2152,15 @@
         <v>12</v>
       </c>
       <c r="E76" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="3">
-        <v>10725</v>
+        <v>10707</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C77" s="4">
         <v>3</v>
@@ -2166,18 +2169,18 @@
         <v>12</v>
       </c>
       <c r="E77" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="3">
-        <v>10762</v>
+        <v>10725</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C78" s="4">
-        <v>1376.8</v>
+        <v>3</v>
       </c>
       <c r="D78" s="3">
         <v>12</v>
@@ -2188,13 +2191,13 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="3">
-        <v>10830</v>
+        <v>10762</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C79" s="4">
-        <v>3</v>
+        <v>1376.8</v>
       </c>
       <c r="D79" s="3">
         <v>12</v>
@@ -2205,30 +2208,30 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="3">
-        <v>10832</v>
+        <v>10830</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C80" s="4">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D80" s="3">
         <v>12</v>
       </c>
       <c r="E80" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="3">
-        <v>10834</v>
+        <v>10832</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C81" s="4">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D81" s="3">
         <v>12</v>
@@ -2239,10 +2242,10 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="3">
-        <v>10836</v>
+        <v>10834</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="C82" s="4">
         <v>5</v>
@@ -2256,13 +2259,13 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="3">
-        <v>10936</v>
+        <v>10836</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="C83" s="4">
-        <v>1093.3499999999999</v>
+        <v>5</v>
       </c>
       <c r="D83" s="3">
         <v>12</v>
@@ -2273,13 +2276,13 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="3">
-        <v>10937</v>
+        <v>10936</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C84" s="4">
-        <v>1183.5</v>
+        <v>1093.3499999999999</v>
       </c>
       <c r="D84" s="3">
         <v>12</v>
@@ -2290,13 +2293,13 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="3">
-        <v>10997</v>
+        <v>10937</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C85" s="4">
-        <v>188.5</v>
+        <v>1183.5</v>
       </c>
       <c r="D85" s="3">
         <v>12</v>
@@ -2307,13 +2310,13 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="3">
-        <v>10998</v>
+        <v>10997</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C86" s="4">
-        <v>790.35299999999995</v>
+        <v>188.5</v>
       </c>
       <c r="D86" s="3">
         <v>12</v>
@@ -2324,13 +2327,13 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="3">
-        <v>11003</v>
+        <v>10998</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C87" s="4">
-        <v>5</v>
+        <v>69.352999999999994</v>
       </c>
       <c r="D87" s="3">
         <v>12</v>
@@ -2341,10 +2344,10 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="3">
-        <v>11105</v>
+        <v>11003</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C88" s="4">
         <v>5</v>
@@ -2358,13 +2361,13 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="3">
-        <v>11106</v>
+        <v>11105</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C89" s="4">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D89" s="3">
         <v>12</v>
@@ -2375,13 +2378,13 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="3">
-        <v>11107</v>
+        <v>11106</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C90" s="4">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D90" s="3">
         <v>12</v>
@@ -2392,13 +2395,13 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="3">
-        <v>11243</v>
+        <v>11107</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C91" s="4">
-        <v>209</v>
+        <v>5</v>
       </c>
       <c r="D91" s="3">
         <v>12</v>
@@ -2409,13 +2412,13 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="3">
-        <v>11269</v>
+        <v>11243</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C92" s="4">
-        <v>10</v>
+        <v>209</v>
       </c>
       <c r="D92" s="3">
         <v>12</v>
@@ -2426,10 +2429,10 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="3">
-        <v>11316</v>
+        <v>11269</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C93" s="4">
         <v>10</v>
@@ -2443,13 +2446,13 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="3">
-        <v>11318</v>
+        <v>11316</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C94" s="4">
-        <v>97.7</v>
+        <v>10</v>
       </c>
       <c r="D94" s="3">
         <v>12</v>
@@ -2460,13 +2463,13 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="3">
-        <v>11362</v>
+        <v>11318</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C95" s="4">
-        <v>5</v>
+        <v>97.7</v>
       </c>
       <c r="D95" s="3">
         <v>12</v>
@@ -2477,13 +2480,13 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="3">
-        <v>11396</v>
+        <v>11362</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C96" s="4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D96" s="3">
         <v>12</v>
@@ -2494,13 +2497,13 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="3">
-        <v>11397</v>
+        <v>11396</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C97" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D97" s="3">
         <v>12</v>
@@ -2511,13 +2514,13 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="3">
-        <v>11444</v>
+        <v>11397</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C98" s="4">
-        <v>230</v>
+        <v>5</v>
       </c>
       <c r="D98" s="3">
         <v>12</v>
@@ -2528,27 +2531,27 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="3">
-        <v>12497</v>
+        <v>11444</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C99" s="4">
-        <v>5</v>
+        <v>230</v>
       </c>
       <c r="D99" s="3">
         <v>12</v>
       </c>
       <c r="E99" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="3">
-        <v>12498</v>
+        <v>12497</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C100" s="4">
         <v>5</v>
@@ -2557,15 +2560,15 @@
         <v>12</v>
       </c>
       <c r="E100" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" s="3">
-        <v>12499</v>
+        <v>12498</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C101" s="4">
         <v>5</v>
@@ -2579,10 +2582,10 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="3">
-        <v>12501</v>
+        <v>12499</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C102" s="4">
         <v>5</v>
@@ -2596,10 +2599,10 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="3">
-        <v>12503</v>
+        <v>12501</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C103" s="4">
         <v>5</v>
@@ -2608,15 +2611,15 @@
         <v>12</v>
       </c>
       <c r="E103" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" s="3">
-        <v>12504</v>
+        <v>12503</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C104" s="4">
         <v>5</v>
@@ -2625,35 +2628,35 @@
         <v>12</v>
       </c>
       <c r="E104" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" s="3">
-        <v>12514</v>
+        <v>12504</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C105" s="4">
-        <v>2329.1</v>
+        <v>5</v>
       </c>
       <c r="D105" s="3">
         <v>12</v>
       </c>
       <c r="E105" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" s="3">
-        <v>12516</v>
+        <v>12514</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C106" s="4">
-        <v>2474.6</v>
+        <v>1500.1</v>
       </c>
       <c r="D106" s="3">
         <v>12</v>
@@ -2664,13 +2667,13 @@
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" s="3">
-        <v>12517</v>
+        <v>12516</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C107" s="4">
-        <v>1553.1</v>
+        <v>2474.6</v>
       </c>
       <c r="D107" s="3">
         <v>12</v>
@@ -2681,13 +2684,13 @@
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="3">
-        <v>12518</v>
+        <v>12517</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C108" s="4">
-        <v>1378.5</v>
+        <v>840.4</v>
       </c>
       <c r="D108" s="3">
         <v>12</v>
@@ -2698,61 +2701,61 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" s="3">
-        <v>12673</v>
+        <v>12518</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C109" s="4">
-        <v>5</v>
+        <v>778.5</v>
       </c>
       <c r="D109" s="3">
         <v>12</v>
       </c>
       <c r="E109" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" s="3">
-        <v>13150</v>
+        <v>12673</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C110" s="4">
-        <v>637.20000000000005</v>
+        <v>5</v>
       </c>
       <c r="D110" s="3">
         <v>12</v>
       </c>
       <c r="E110" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" s="3">
-        <v>14365</v>
+        <v>13150</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C111" s="4">
-        <v>2</v>
+        <v>637.20000000000005</v>
       </c>
       <c r="D111" s="3">
         <v>12</v>
       </c>
       <c r="E111" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="3">
-        <v>14366</v>
+        <v>14365</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C112" s="4">
         <v>2</v>
@@ -2766,10 +2769,10 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" s="3">
-        <v>14367</v>
+        <v>14366</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C113" s="4">
         <v>2</v>
@@ -2778,52 +2781,52 @@
         <v>12</v>
       </c>
       <c r="E113" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="3">
-        <v>14928</v>
+        <v>14367</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C114" s="4">
-        <v>7.5</v>
+        <v>2</v>
       </c>
       <c r="D114" s="3">
         <v>12</v>
       </c>
       <c r="E114" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="3">
-        <v>15405</v>
+        <v>14928</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C115" s="4">
-        <v>225</v>
+        <v>7.5</v>
       </c>
       <c r="D115" s="3">
         <v>12</v>
       </c>
       <c r="E115" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" s="3">
-        <v>16460</v>
+        <v>15405</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C116" s="4">
-        <v>1</v>
+        <v>225</v>
       </c>
       <c r="D116" s="3">
         <v>12</v>
@@ -2834,10 +2837,10 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" s="3">
-        <v>16461</v>
+        <v>16460</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C117" s="4">
         <v>1</v>
@@ -2851,10 +2854,10 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" s="3">
-        <v>16462</v>
+        <v>16461</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C118" s="4">
         <v>1</v>
@@ -2868,30 +2871,30 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" s="3">
-        <v>17075</v>
+        <v>16462</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C119" s="4">
-        <v>1832</v>
+        <v>1</v>
       </c>
       <c r="D119" s="3">
         <v>12</v>
       </c>
       <c r="E119" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" s="3">
-        <v>17076</v>
+        <v>17075</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C120" s="4">
-        <v>1141.8</v>
+        <v>1632</v>
       </c>
       <c r="D120" s="3">
         <v>12</v>
@@ -2902,19 +2905,19 @@
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" s="3">
-        <v>17863</v>
+        <v>17076</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="C121" s="4">
-        <v>500</v>
+        <v>941.8</v>
       </c>
       <c r="D121" s="3">
         <v>12</v>
       </c>
       <c r="E121" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
@@ -2923,7 +2926,6 @@
       <c r="C122" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E122" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="9999" orientation="landscape"/>

--- a/data-source/ESTOQUETRANSFER.xlsx
+++ b/data-source/ESTOQUETRANSFER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/TRANSFER-ANALISE/data-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="8_{20405EE4-7847-4583-ADA9-6FB66CEB9340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ECC96B09-B354-4EDD-ABF2-EAC7B159E980}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="8_{20405EE4-7847-4583-ADA9-6FB66CEB9340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF1B0C95-5262-4915-9EDE-63AF2436D93B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="130">
   <si>
     <t>Produto</t>
   </si>
@@ -153,9 +153,6 @@
     <t>TRANSFER TOTAL METALIC FILM GRAFITE QT-339A - AMERICA ASIA</t>
   </si>
   <si>
-    <t>TRANSFER TOTAL METALIC FILM GOLD QT-HB-056A - AMERICA ASIA</t>
-  </si>
-  <si>
     <t>TRANSFER TOTAL METALIC FILM SILVER QT-001A - AMERICA ASIA</t>
   </si>
   <si>
@@ -385,9 +382,6 @@
   </si>
   <si>
     <t>TRANSFER UNITRANS 115 - PALAGI</t>
-  </si>
-  <si>
-    <t>QT-200A FULL TRANSFER - CAFÉ</t>
   </si>
   <si>
     <t>QT-077A FULL TRANSFER - WHISKY</t>
@@ -531,6 +525,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -874,10 +872,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -894,7 +892,7 @@
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -911,7 +909,7 @@
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -928,7 +926,7 @@
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -945,7 +943,7 @@
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -962,7 +960,7 @@
         <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -979,7 +977,7 @@
         <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -996,7 +994,7 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -1013,7 +1011,7 @@
         <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -1030,7 +1028,7 @@
         <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -1047,7 +1045,7 @@
         <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -1064,7 +1062,7 @@
         <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -1081,7 +1079,7 @@
         <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -1098,7 +1096,7 @@
         <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -1115,7 +1113,7 @@
         <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -1132,7 +1130,7 @@
         <v>12</v>
       </c>
       <c r="E16" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -1149,7 +1147,7 @@
         <v>12</v>
       </c>
       <c r="E17" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -1166,7 +1164,7 @@
         <v>12</v>
       </c>
       <c r="E18" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -1183,7 +1181,7 @@
         <v>12</v>
       </c>
       <c r="E19" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -1200,7 +1198,7 @@
         <v>12</v>
       </c>
       <c r="E20" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -1217,7 +1215,7 @@
         <v>12</v>
       </c>
       <c r="E21" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -1234,7 +1232,7 @@
         <v>12</v>
       </c>
       <c r="E22" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -1251,7 +1249,7 @@
         <v>12</v>
       </c>
       <c r="E23" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -1259,61 +1257,61 @@
         <v>4413</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C24" s="4">
-        <v>500</v>
+        <v>10.3</v>
       </c>
       <c r="D24" s="3">
         <v>12</v>
       </c>
       <c r="E24" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
-        <v>4423</v>
+        <v>4413</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>25</v>
+        <v>128</v>
       </c>
       <c r="C25" s="4">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="D25" s="3">
         <v>12</v>
       </c>
       <c r="E25" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
-        <v>4721</v>
+        <v>4423</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C26" s="4">
-        <v>1701.5</v>
+        <v>100</v>
       </c>
       <c r="D26" s="3">
         <v>12</v>
       </c>
       <c r="E26" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
-        <v>4722</v>
+        <v>4721</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C27" s="4">
-        <v>3883.5</v>
+        <v>1701.5</v>
       </c>
       <c r="D27" s="3">
         <v>12</v>
@@ -1324,172 +1322,172 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
-        <v>4723</v>
+        <v>4722</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C28" s="4">
-        <v>2974.5</v>
+        <v>3883.5</v>
       </c>
       <c r="D28" s="3">
         <v>12</v>
       </c>
       <c r="E28" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
-        <v>5024</v>
+        <v>4723</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C29" s="4">
-        <v>3325.5</v>
+        <v>2974.5</v>
       </c>
       <c r="D29" s="3">
         <v>12</v>
       </c>
       <c r="E29" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
-        <v>5025</v>
+        <v>5024</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C30" s="4">
-        <v>3064.5</v>
+        <v>3325.5</v>
       </c>
       <c r="D30" s="3">
         <v>12</v>
       </c>
       <c r="E30" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
-        <v>5437</v>
+        <v>5025</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C31" s="4">
-        <v>70</v>
+        <v>3064.5</v>
       </c>
       <c r="D31" s="3">
         <v>12</v>
       </c>
       <c r="E31" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
-        <v>5861</v>
+        <v>5437</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C32" s="4">
-        <v>328</v>
+        <v>70</v>
       </c>
       <c r="D32" s="3">
         <v>12</v>
       </c>
       <c r="E32" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
-        <v>5931</v>
+        <v>5861</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C33" s="4">
-        <v>11</v>
+        <v>328</v>
       </c>
       <c r="D33" s="3">
         <v>12</v>
       </c>
       <c r="E33" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
-        <v>5932</v>
+        <v>5931</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C34" s="4">
-        <v>80</v>
+        <v>11</v>
       </c>
       <c r="D34" s="3">
         <v>12</v>
       </c>
       <c r="E34" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
-        <v>6248</v>
+        <v>5932</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C35" s="4">
-        <v>350</v>
+        <v>80</v>
       </c>
       <c r="D35" s="3">
         <v>12</v>
       </c>
       <c r="E35" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
-        <v>6560</v>
+        <v>6248</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C36" s="4">
-        <v>2083.5</v>
+        <v>350</v>
       </c>
       <c r="D36" s="3">
         <v>12</v>
       </c>
       <c r="E36" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
-        <v>7425</v>
+        <v>6560</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C37" s="4">
-        <v>300</v>
+        <v>2083.5</v>
       </c>
       <c r="D37" s="3">
         <v>12</v>
       </c>
       <c r="E37" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
@@ -1500,30 +1498,30 @@
         <v>37</v>
       </c>
       <c r="C38" s="4">
-        <v>7988.78</v>
+        <v>300</v>
       </c>
       <c r="D38" s="3">
         <v>12</v>
       </c>
       <c r="E38" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
-        <v>7484</v>
+        <v>7425</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C39" s="4">
-        <v>4470</v>
+        <v>7588.78</v>
       </c>
       <c r="D39" s="3">
         <v>12</v>
       </c>
       <c r="E39" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -1531,16 +1529,16 @@
         <v>7485</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C40" s="4">
-        <v>5404.5</v>
+        <v>4404.5</v>
       </c>
       <c r="D40" s="3">
         <v>12</v>
       </c>
       <c r="E40" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
@@ -1548,7 +1546,7 @@
         <v>7486</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C41" s="4">
         <v>17480.5</v>
@@ -1557,7 +1555,7 @@
         <v>12</v>
       </c>
       <c r="E41" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
@@ -1565,7 +1563,7 @@
         <v>7771</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C42" s="4">
         <v>1191</v>
@@ -1574,7 +1572,7 @@
         <v>12</v>
       </c>
       <c r="E42" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
@@ -1582,7 +1580,7 @@
         <v>8111</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C43" s="4">
         <v>383</v>
@@ -1591,7 +1589,7 @@
         <v>12</v>
       </c>
       <c r="E43" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
@@ -1599,7 +1597,7 @@
         <v>8175</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C44" s="4">
         <v>2377.5</v>
@@ -1608,7 +1606,7 @@
         <v>12</v>
       </c>
       <c r="E44" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
@@ -1616,7 +1614,7 @@
         <v>8418</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C45" s="4">
         <v>954.5</v>
@@ -1625,7 +1623,7 @@
         <v>12</v>
       </c>
       <c r="E45" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
@@ -1633,7 +1631,7 @@
         <v>8472</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C46" s="4">
         <v>10</v>
@@ -1642,7 +1640,7 @@
         <v>12</v>
       </c>
       <c r="E46" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
@@ -1650,7 +1648,7 @@
         <v>8612</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C47" s="4">
         <v>600</v>
@@ -1659,7 +1657,7 @@
         <v>12</v>
       </c>
       <c r="E47" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
@@ -1667,7 +1665,7 @@
         <v>8613</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C48" s="4">
         <v>410</v>
@@ -1676,7 +1674,7 @@
         <v>12</v>
       </c>
       <c r="E48" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
@@ -1684,7 +1682,7 @@
         <v>8645</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C49" s="4">
         <v>35</v>
@@ -1693,7 +1691,7 @@
         <v>12</v>
       </c>
       <c r="E49" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
@@ -1701,7 +1699,7 @@
         <v>8713</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C50" s="4">
         <v>463</v>
@@ -1710,7 +1708,7 @@
         <v>12</v>
       </c>
       <c r="E50" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
@@ -1718,7 +1716,7 @@
         <v>9000</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C51" s="4">
         <v>8.5</v>
@@ -1727,7 +1725,7 @@
         <v>12</v>
       </c>
       <c r="E51" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
@@ -1735,7 +1733,7 @@
         <v>9009</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C52" s="4">
         <v>60</v>
@@ -1744,7 +1742,7 @@
         <v>12</v>
       </c>
       <c r="E52" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
@@ -1752,7 +1750,7 @@
         <v>9336</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C53" s="4">
         <v>750.1</v>
@@ -1761,7 +1759,7 @@
         <v>12</v>
       </c>
       <c r="E53" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
@@ -1769,7 +1767,7 @@
         <v>9396</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C54" s="4">
         <v>435.5</v>
@@ -1778,7 +1776,7 @@
         <v>12</v>
       </c>
       <c r="E54" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
@@ -1786,7 +1784,7 @@
         <v>9397</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C55" s="4">
         <v>1499</v>
@@ -1795,7 +1793,7 @@
         <v>12</v>
       </c>
       <c r="E55" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
@@ -1803,7 +1801,7 @@
         <v>9398</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C56" s="4">
         <v>1199</v>
@@ -1812,7 +1810,7 @@
         <v>12</v>
       </c>
       <c r="E56" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
@@ -1820,7 +1818,7 @@
         <v>9399</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C57" s="4">
         <v>594</v>
@@ -1829,7 +1827,7 @@
         <v>12</v>
       </c>
       <c r="E57" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
@@ -1837,7 +1835,7 @@
         <v>9430</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C58" s="4">
         <v>25</v>
@@ -1846,7 +1844,7 @@
         <v>12</v>
       </c>
       <c r="E58" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
@@ -1854,7 +1852,7 @@
         <v>9430</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C59" s="4">
         <v>2327.8000000000002</v>
@@ -1863,7 +1861,7 @@
         <v>12</v>
       </c>
       <c r="E59" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
@@ -1871,7 +1869,7 @@
         <v>9476</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C60" s="4">
         <v>1768.5</v>
@@ -1880,7 +1878,7 @@
         <v>12</v>
       </c>
       <c r="E60" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
@@ -1888,7 +1886,7 @@
         <v>9591</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C61" s="4">
         <v>5</v>
@@ -1897,7 +1895,7 @@
         <v>12</v>
       </c>
       <c r="E61" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
@@ -1905,7 +1903,7 @@
         <v>9633</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C62" s="4">
         <v>400</v>
@@ -1914,7 +1912,7 @@
         <v>12</v>
       </c>
       <c r="E62" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
@@ -1922,7 +1920,7 @@
         <v>9804</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C63" s="4">
         <v>1058</v>
@@ -1931,7 +1929,7 @@
         <v>12</v>
       </c>
       <c r="E63" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
@@ -1939,7 +1937,7 @@
         <v>9805</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C64" s="4">
         <v>40</v>
@@ -1948,7 +1946,7 @@
         <v>12</v>
       </c>
       <c r="E64" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
@@ -1956,7 +1954,7 @@
         <v>10026</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C65" s="4">
         <v>5</v>
@@ -1965,7 +1963,7 @@
         <v>12</v>
       </c>
       <c r="E65" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
@@ -1973,7 +1971,7 @@
         <v>10027</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C66" s="4">
         <v>5</v>
@@ -1982,7 +1980,7 @@
         <v>12</v>
       </c>
       <c r="E66" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
@@ -1990,7 +1988,7 @@
         <v>10028</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C67" s="4">
         <v>8</v>
@@ -1999,7 +1997,7 @@
         <v>12</v>
       </c>
       <c r="E67" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
@@ -2007,7 +2005,7 @@
         <v>10031</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C68" s="4">
         <v>15</v>
@@ -2016,7 +2014,7 @@
         <v>12</v>
       </c>
       <c r="E68" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
@@ -2024,7 +2022,7 @@
         <v>10042</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C69" s="4">
         <v>100</v>
@@ -2033,7 +2031,7 @@
         <v>12</v>
       </c>
       <c r="E69" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
@@ -2041,7 +2039,7 @@
         <v>10042</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C70" s="4">
         <v>945</v>
@@ -2050,7 +2048,7 @@
         <v>12</v>
       </c>
       <c r="E70" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
@@ -2058,7 +2056,7 @@
         <v>10044</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C71" s="4">
         <v>80</v>
@@ -2067,7 +2065,7 @@
         <v>12</v>
       </c>
       <c r="E71" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
@@ -2075,7 +2073,7 @@
         <v>10080</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C72" s="4">
         <v>50</v>
@@ -2084,7 +2082,7 @@
         <v>12</v>
       </c>
       <c r="E72" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
@@ -2092,7 +2090,7 @@
         <v>10254</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C73" s="4">
         <v>70</v>
@@ -2101,7 +2099,7 @@
         <v>12</v>
       </c>
       <c r="E73" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
@@ -2109,7 +2107,7 @@
         <v>10318</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C74" s="4">
         <v>50</v>
@@ -2118,7 +2116,7 @@
         <v>12</v>
       </c>
       <c r="E74" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
@@ -2126,7 +2124,7 @@
         <v>10362</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C75" s="4">
         <v>10</v>
@@ -2135,7 +2133,7 @@
         <v>12</v>
       </c>
       <c r="E75" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
@@ -2143,7 +2141,7 @@
         <v>10692</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C76" s="4">
         <v>3</v>
@@ -2152,7 +2150,7 @@
         <v>12</v>
       </c>
       <c r="E76" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
@@ -2160,7 +2158,7 @@
         <v>10707</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C77" s="4">
         <v>3</v>
@@ -2169,7 +2167,7 @@
         <v>12</v>
       </c>
       <c r="E77" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
@@ -2177,7 +2175,7 @@
         <v>10725</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C78" s="4">
         <v>3</v>
@@ -2186,7 +2184,7 @@
         <v>12</v>
       </c>
       <c r="E78" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
@@ -2194,7 +2192,7 @@
         <v>10762</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C79" s="4">
         <v>1376.8</v>
@@ -2203,7 +2201,7 @@
         <v>12</v>
       </c>
       <c r="E79" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
@@ -2211,7 +2209,7 @@
         <v>10830</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C80" s="4">
         <v>3</v>
@@ -2220,7 +2218,7 @@
         <v>12</v>
       </c>
       <c r="E80" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
@@ -2228,16 +2226,16 @@
         <v>10832</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C81" s="4">
-        <v>15</v>
+        <v>1015</v>
       </c>
       <c r="D81" s="3">
         <v>12</v>
       </c>
       <c r="E81" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
@@ -2245,7 +2243,7 @@
         <v>10834</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C82" s="4">
         <v>5</v>
@@ -2254,7 +2252,7 @@
         <v>12</v>
       </c>
       <c r="E82" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
@@ -2262,7 +2260,7 @@
         <v>10836</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C83" s="4">
         <v>5</v>
@@ -2271,7 +2269,7 @@
         <v>12</v>
       </c>
       <c r="E83" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
@@ -2279,7 +2277,7 @@
         <v>10936</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C84" s="4">
         <v>1093.3499999999999</v>
@@ -2288,7 +2286,7 @@
         <v>12</v>
       </c>
       <c r="E84" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
@@ -2296,7 +2294,7 @@
         <v>10937</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C85" s="4">
         <v>1183.5</v>
@@ -2305,7 +2303,7 @@
         <v>12</v>
       </c>
       <c r="E85" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
@@ -2313,7 +2311,7 @@
         <v>10997</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C86" s="4">
         <v>188.5</v>
@@ -2322,7 +2320,7 @@
         <v>12</v>
       </c>
       <c r="E86" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
@@ -2330,7 +2328,7 @@
         <v>10998</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C87" s="4">
         <v>69.352999999999994</v>
@@ -2339,7 +2337,7 @@
         <v>12</v>
       </c>
       <c r="E87" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
@@ -2347,7 +2345,7 @@
         <v>11003</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C88" s="4">
         <v>5</v>
@@ -2356,7 +2354,7 @@
         <v>12</v>
       </c>
       <c r="E88" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
@@ -2364,7 +2362,7 @@
         <v>11105</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C89" s="4">
         <v>5</v>
@@ -2373,7 +2371,7 @@
         <v>12</v>
       </c>
       <c r="E89" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
@@ -2381,7 +2379,7 @@
         <v>11106</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C90" s="4">
         <v>20</v>
@@ -2390,7 +2388,7 @@
         <v>12</v>
       </c>
       <c r="E90" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
@@ -2398,7 +2396,7 @@
         <v>11107</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C91" s="4">
         <v>5</v>
@@ -2407,7 +2405,7 @@
         <v>12</v>
       </c>
       <c r="E91" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
@@ -2415,7 +2413,7 @@
         <v>11243</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C92" s="4">
         <v>209</v>
@@ -2424,7 +2422,7 @@
         <v>12</v>
       </c>
       <c r="E92" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
@@ -2432,7 +2430,7 @@
         <v>11269</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C93" s="4">
         <v>10</v>
@@ -2441,7 +2439,7 @@
         <v>12</v>
       </c>
       <c r="E93" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
@@ -2449,7 +2447,7 @@
         <v>11316</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C94" s="4">
         <v>10</v>
@@ -2458,7 +2456,7 @@
         <v>12</v>
       </c>
       <c r="E94" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
@@ -2466,7 +2464,7 @@
         <v>11318</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C95" s="4">
         <v>97.7</v>
@@ -2475,7 +2473,7 @@
         <v>12</v>
       </c>
       <c r="E95" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
@@ -2483,7 +2481,7 @@
         <v>11362</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C96" s="4">
         <v>5</v>
@@ -2492,7 +2490,7 @@
         <v>12</v>
       </c>
       <c r="E96" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
@@ -2500,7 +2498,7 @@
         <v>11396</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C97" s="4">
         <v>7</v>
@@ -2509,7 +2507,7 @@
         <v>12</v>
       </c>
       <c r="E97" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
@@ -2517,7 +2515,7 @@
         <v>11397</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C98" s="4">
         <v>5</v>
@@ -2526,7 +2524,7 @@
         <v>12</v>
       </c>
       <c r="E98" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
@@ -2534,7 +2532,7 @@
         <v>11444</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C99" s="4">
         <v>230</v>
@@ -2543,7 +2541,7 @@
         <v>12</v>
       </c>
       <c r="E99" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
@@ -2551,7 +2549,7 @@
         <v>12497</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C100" s="4">
         <v>5</v>
@@ -2560,7 +2558,7 @@
         <v>12</v>
       </c>
       <c r="E100" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
@@ -2568,7 +2566,7 @@
         <v>12498</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C101" s="4">
         <v>5</v>
@@ -2577,7 +2575,7 @@
         <v>12</v>
       </c>
       <c r="E101" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
@@ -2585,7 +2583,7 @@
         <v>12499</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C102" s="4">
         <v>5</v>
@@ -2594,7 +2592,7 @@
         <v>12</v>
       </c>
       <c r="E102" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
@@ -2602,7 +2600,7 @@
         <v>12501</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C103" s="4">
         <v>5</v>
@@ -2611,7 +2609,7 @@
         <v>12</v>
       </c>
       <c r="E103" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
@@ -2619,7 +2617,7 @@
         <v>12503</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C104" s="4">
         <v>5</v>
@@ -2628,7 +2626,7 @@
         <v>12</v>
       </c>
       <c r="E104" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
@@ -2636,7 +2634,7 @@
         <v>12504</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C105" s="4">
         <v>5</v>
@@ -2645,7 +2643,7 @@
         <v>12</v>
       </c>
       <c r="E105" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
@@ -2653,7 +2651,7 @@
         <v>12514</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C106" s="4">
         <v>1500.1</v>
@@ -2662,7 +2660,7 @@
         <v>12</v>
       </c>
       <c r="E106" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
@@ -2670,16 +2668,16 @@
         <v>12516</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C107" s="4">
-        <v>2474.6</v>
+        <v>2464.6</v>
       </c>
       <c r="D107" s="3">
         <v>12</v>
       </c>
       <c r="E107" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
@@ -2687,7 +2685,7 @@
         <v>12517</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C108" s="4">
         <v>840.4</v>
@@ -2696,7 +2694,7 @@
         <v>12</v>
       </c>
       <c r="E108" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
@@ -2704,7 +2702,7 @@
         <v>12518</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C109" s="4">
         <v>778.5</v>
@@ -2713,7 +2711,7 @@
         <v>12</v>
       </c>
       <c r="E109" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
@@ -2721,7 +2719,7 @@
         <v>12673</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C110" s="4">
         <v>5</v>
@@ -2730,7 +2728,7 @@
         <v>12</v>
       </c>
       <c r="E110" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
@@ -2738,7 +2736,7 @@
         <v>13150</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C111" s="4">
         <v>637.20000000000005</v>
@@ -2747,7 +2745,7 @@
         <v>12</v>
       </c>
       <c r="E111" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
@@ -2755,7 +2753,7 @@
         <v>14365</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C112" s="4">
         <v>2</v>
@@ -2764,7 +2762,7 @@
         <v>12</v>
       </c>
       <c r="E112" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
@@ -2772,7 +2770,7 @@
         <v>14366</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C113" s="4">
         <v>2</v>
@@ -2781,7 +2779,7 @@
         <v>12</v>
       </c>
       <c r="E113" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
@@ -2789,7 +2787,7 @@
         <v>14367</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C114" s="4">
         <v>2</v>
@@ -2798,7 +2796,7 @@
         <v>12</v>
       </c>
       <c r="E114" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
@@ -2806,7 +2804,7 @@
         <v>14928</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C115" s="4">
         <v>7.5</v>
@@ -2815,7 +2813,7 @@
         <v>12</v>
       </c>
       <c r="E115" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
@@ -2823,7 +2821,7 @@
         <v>15405</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C116" s="4">
         <v>225</v>
@@ -2832,7 +2830,7 @@
         <v>12</v>
       </c>
       <c r="E116" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
@@ -2840,7 +2838,7 @@
         <v>16460</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C117" s="4">
         <v>1</v>
@@ -2849,7 +2847,7 @@
         <v>12</v>
       </c>
       <c r="E117" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
@@ -2857,7 +2855,7 @@
         <v>16461</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C118" s="4">
         <v>1</v>
@@ -2866,7 +2864,7 @@
         <v>12</v>
       </c>
       <c r="E118" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
@@ -2874,7 +2872,7 @@
         <v>16462</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C119" s="4">
         <v>1</v>
@@ -2883,42 +2881,31 @@
         <v>12</v>
       </c>
       <c r="E119" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" s="3">
-        <v>17075</v>
+        <v>17076</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C120" s="4">
-        <v>1632</v>
+        <v>540.79999999999995</v>
       </c>
       <c r="D120" s="3">
         <v>12</v>
       </c>
       <c r="E120" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A121" s="3">
-        <v>17076</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C121" s="4">
-        <v>941.8</v>
-      </c>
-      <c r="D121" s="3">
-        <v>12</v>
-      </c>
-      <c r="E121" t="s">
-        <v>120</v>
-      </c>
+      <c r="A121" s="3"/>
+      <c r="B121" s="1"/>
+      <c r="C121" s="4"/>
+      <c r="D121" s="3"/>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" s="3"/>

--- a/data-source/ESTOQUETRANSFER.xlsx
+++ b/data-source/ESTOQUETRANSFER.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/TRANSFER-ANALISE/data-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="8_{20405EE4-7847-4583-ADA9-6FB66CEB9340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF1B0C95-5262-4915-9EDE-63AF2436D93B}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="14_{33D7B264-E024-46AE-875B-F5C883B9D1BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{637C540A-A232-4A62-B3C2-95F04CAAD9D7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha!$A$1:$E$122</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha!$A$1:$E$120</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Planilha!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="135">
   <si>
     <t>Produto</t>
   </si>
@@ -351,9 +351,6 @@
     <t>TRANSFER 99-5-4 PARCIAL FILM - GRAPHITE</t>
   </si>
   <si>
-    <t>TRANSFER 99-5-4 PARCIAL FILM - ROSE GOLD</t>
-  </si>
-  <si>
     <t>TRANSFER LAM LASER ROSE NEW 2</t>
   </si>
   <si>
@@ -427,6 +424,24 @@
   </si>
   <si>
     <t>PONTILHADO</t>
+  </si>
+  <si>
+    <t>TRANSFER TOTAL METALIC FILM GOLD QT-HB-056A - AMERICA ASIA</t>
+  </si>
+  <si>
+    <t>QT-467A METALIC FILM (FULL TRANSFER) - BRONZE</t>
+  </si>
+  <si>
+    <t>TRANSFER 99-5-4 PARCIAL FOIL - LT GOLD</t>
+  </si>
+  <si>
+    <t>QT-200A FULL TRANSFER - CAFÉ</t>
+  </si>
+  <si>
+    <t>PROTECTION FILM 25UM - AMERICA ASIA</t>
+  </si>
+  <si>
+    <t>PROTECTION</t>
   </si>
 </sst>
 </file>
@@ -525,10 +540,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -851,13 +862,13 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E122"/>
+  <dimension ref="A1:E127"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="62.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -872,10 +883,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>116</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -886,13 +897,13 @@
         <v>3</v>
       </c>
       <c r="C2" s="4">
-        <v>529.5</v>
+        <v>27.5</v>
       </c>
       <c r="D2" s="3">
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -909,7 +920,7 @@
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -926,7 +937,7 @@
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -943,7 +954,7 @@
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -960,7 +971,7 @@
         <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -977,7 +988,7 @@
         <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -994,7 +1005,7 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -1011,7 +1022,7 @@
         <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -1028,7 +1039,7 @@
         <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -1045,7 +1056,7 @@
         <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -1062,7 +1073,7 @@
         <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -1079,7 +1090,7 @@
         <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -1096,7 +1107,7 @@
         <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -1113,7 +1124,7 @@
         <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -1130,7 +1141,7 @@
         <v>12</v>
       </c>
       <c r="E16" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -1147,7 +1158,7 @@
         <v>12</v>
       </c>
       <c r="E17" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -1164,7 +1175,7 @@
         <v>12</v>
       </c>
       <c r="E18" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -1181,7 +1192,7 @@
         <v>12</v>
       </c>
       <c r="E19" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -1198,7 +1209,7 @@
         <v>12</v>
       </c>
       <c r="E20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -1215,7 +1226,7 @@
         <v>12</v>
       </c>
       <c r="E21" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -1232,7 +1243,7 @@
         <v>12</v>
       </c>
       <c r="E22" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -1249,7 +1260,7 @@
         <v>12</v>
       </c>
       <c r="E23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -1257,7 +1268,7 @@
         <v>4413</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C24" s="4">
         <v>10.3</v>
@@ -1266,7 +1277,7 @@
         <v>12</v>
       </c>
       <c r="E24" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -1274,16 +1285,16 @@
         <v>4413</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C25" s="4">
+        <v>2515</v>
+      </c>
+      <c r="D25" s="3">
+        <v>12</v>
+      </c>
+      <c r="E25" t="s">
         <v>128</v>
-      </c>
-      <c r="C25" s="4">
-        <v>500</v>
-      </c>
-      <c r="D25" s="3">
-        <v>12</v>
-      </c>
-      <c r="E25" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
@@ -1300,7 +1311,7 @@
         <v>12</v>
       </c>
       <c r="E26" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -1317,7 +1328,7 @@
         <v>12</v>
       </c>
       <c r="E27" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -1334,7 +1345,7 @@
         <v>12</v>
       </c>
       <c r="E28" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
@@ -1351,7 +1362,7 @@
         <v>12</v>
       </c>
       <c r="E29" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -1368,7 +1379,7 @@
         <v>12</v>
       </c>
       <c r="E30" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
@@ -1385,7 +1396,7 @@
         <v>12</v>
       </c>
       <c r="E31" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
@@ -1402,7 +1413,7 @@
         <v>12</v>
       </c>
       <c r="E32" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
@@ -1419,7 +1430,7 @@
         <v>12</v>
       </c>
       <c r="E33" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
@@ -1436,7 +1447,7 @@
         <v>12</v>
       </c>
       <c r="E34" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
@@ -1453,7 +1464,7 @@
         <v>12</v>
       </c>
       <c r="E35" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
@@ -1470,7 +1481,7 @@
         <v>12</v>
       </c>
       <c r="E36" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
@@ -1487,7 +1498,7 @@
         <v>12</v>
       </c>
       <c r="E37" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
@@ -1504,7 +1515,7 @@
         <v>12</v>
       </c>
       <c r="E38" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
@@ -1521,239 +1532,239 @@
         <v>12</v>
       </c>
       <c r="E39" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
-        <v>7485</v>
+        <v>7484</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>38</v>
+        <v>129</v>
       </c>
       <c r="C40" s="4">
-        <v>4404.5</v>
+        <v>1272</v>
       </c>
       <c r="D40" s="3">
         <v>12</v>
       </c>
       <c r="E40" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
-        <v>7486</v>
+        <v>7485</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C41" s="4">
-        <v>17480.5</v>
+        <v>2404.5</v>
       </c>
       <c r="D41" s="3">
         <v>12</v>
       </c>
       <c r="E41" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
-        <v>7771</v>
+        <v>7486</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C42" s="4">
-        <v>1191</v>
+        <v>15880.5</v>
       </c>
       <c r="D42" s="3">
         <v>12</v>
       </c>
       <c r="E42" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
-        <v>8111</v>
+        <v>7771</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C43" s="4">
-        <v>383</v>
+        <v>1191</v>
       </c>
       <c r="D43" s="3">
         <v>12</v>
       </c>
       <c r="E43" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
-        <v>8175</v>
+        <v>8111</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C44" s="4">
-        <v>2377.5</v>
+        <v>383</v>
       </c>
       <c r="D44" s="3">
         <v>12</v>
       </c>
       <c r="E44" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
-        <v>8418</v>
+        <v>8175</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C45" s="4">
-        <v>954.5</v>
+        <v>2377.5</v>
       </c>
       <c r="D45" s="3">
         <v>12</v>
       </c>
       <c r="E45" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
-        <v>8472</v>
+        <v>8418</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C46" s="4">
-        <v>10</v>
+        <v>954.5</v>
       </c>
       <c r="D46" s="3">
         <v>12</v>
       </c>
       <c r="E46" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
-        <v>8612</v>
+        <v>8472</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C47" s="4">
-        <v>600</v>
+        <v>10</v>
       </c>
       <c r="D47" s="3">
         <v>12</v>
       </c>
       <c r="E47" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
-        <v>8613</v>
+        <v>8612</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C48" s="4">
-        <v>410</v>
+        <v>600</v>
       </c>
       <c r="D48" s="3">
         <v>12</v>
       </c>
       <c r="E48" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
-        <v>8645</v>
+        <v>8613</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C49" s="4">
-        <v>35</v>
+        <v>410</v>
       </c>
       <c r="D49" s="3">
         <v>12</v>
       </c>
       <c r="E49" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
-        <v>8713</v>
+        <v>8645</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C50" s="4">
-        <v>463</v>
+        <v>35</v>
       </c>
       <c r="D50" s="3">
         <v>12</v>
       </c>
       <c r="E50" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
-        <v>9000</v>
+        <v>8713</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C51" s="4">
-        <v>8.5</v>
+        <v>463</v>
       </c>
       <c r="D51" s="3">
         <v>12</v>
       </c>
       <c r="E51" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
-        <v>9009</v>
+        <v>9000</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C52" s="4">
-        <v>60</v>
+        <v>528.5</v>
       </c>
       <c r="D52" s="3">
         <v>12</v>
       </c>
       <c r="E52" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
-        <v>9336</v>
+        <v>9009</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C53" s="4">
-        <v>750.1</v>
+        <v>60</v>
       </c>
       <c r="D53" s="3">
         <v>12</v>
@@ -1764,87 +1775,87 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
-        <v>9396</v>
+        <v>9336</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C54" s="4">
-        <v>435.5</v>
+        <v>750.1</v>
       </c>
       <c r="D54" s="3">
         <v>12</v>
       </c>
       <c r="E54" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
-        <v>9397</v>
+        <v>9396</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C55" s="4">
-        <v>1499</v>
+        <v>125.5</v>
       </c>
       <c r="D55" s="3">
         <v>12</v>
       </c>
       <c r="E55" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
-        <v>9398</v>
+        <v>9397</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C56" s="4">
-        <v>1199</v>
+        <v>1299</v>
       </c>
       <c r="D56" s="3">
         <v>12</v>
       </c>
       <c r="E56" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
-        <v>9399</v>
+        <v>9398</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C57" s="4">
-        <v>594</v>
+        <v>1199</v>
       </c>
       <c r="D57" s="3">
         <v>12</v>
       </c>
       <c r="E57" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
-        <v>9430</v>
+        <v>9399</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C58" s="4">
-        <v>25</v>
+        <v>594</v>
       </c>
       <c r="D58" s="3">
         <v>12</v>
       </c>
       <c r="E58" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
@@ -1855,123 +1866,123 @@
         <v>56</v>
       </c>
       <c r="C59" s="4">
-        <v>2327.8000000000002</v>
+        <v>25</v>
       </c>
       <c r="D59" s="3">
         <v>12</v>
       </c>
       <c r="E59" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
-        <v>9476</v>
+        <v>9430</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C60" s="4">
-        <v>1768.5</v>
+        <v>2327.8000000000002</v>
       </c>
       <c r="D60" s="3">
         <v>12</v>
       </c>
       <c r="E60" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
-        <v>9591</v>
+        <v>9476</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C61" s="4">
-        <v>5</v>
+        <v>1768.5</v>
       </c>
       <c r="D61" s="3">
         <v>12</v>
       </c>
       <c r="E61" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
-        <v>9633</v>
+        <v>9591</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C62" s="4">
-        <v>400</v>
+        <v>5</v>
       </c>
       <c r="D62" s="3">
         <v>12</v>
       </c>
       <c r="E62" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
-        <v>9804</v>
+        <v>9633</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C63" s="4">
-        <v>1058</v>
+        <v>400</v>
       </c>
       <c r="D63" s="3">
         <v>12</v>
       </c>
       <c r="E63" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
-        <v>9805</v>
+        <v>9804</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C64" s="4">
-        <v>40</v>
+        <v>1058</v>
       </c>
       <c r="D64" s="3">
         <v>12</v>
       </c>
       <c r="E64" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
-        <v>10026</v>
+        <v>9805</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C65" s="4">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="D65" s="3">
         <v>12</v>
       </c>
       <c r="E65" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="3">
-        <v>10027</v>
+        <v>10026</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C66" s="4">
         <v>5</v>
@@ -1980,58 +1991,58 @@
         <v>12</v>
       </c>
       <c r="E66" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
-        <v>10028</v>
+        <v>10027</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C67" s="4">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D67" s="3">
         <v>12</v>
       </c>
       <c r="E67" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
-        <v>10031</v>
+        <v>10028</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C68" s="4">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D68" s="3">
         <v>12</v>
       </c>
       <c r="E68" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="3">
-        <v>10042</v>
+        <v>10031</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C69" s="4">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="D69" s="3">
         <v>12</v>
       </c>
       <c r="E69" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
@@ -2042,140 +2053,140 @@
         <v>66</v>
       </c>
       <c r="C70" s="4">
-        <v>945</v>
+        <v>100</v>
       </c>
       <c r="D70" s="3">
         <v>12</v>
       </c>
       <c r="E70" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="3">
-        <v>10044</v>
+        <v>10042</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C71" s="4">
-        <v>80</v>
+        <v>945</v>
       </c>
       <c r="D71" s="3">
         <v>12</v>
       </c>
       <c r="E71" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="3">
-        <v>10080</v>
+        <v>10044</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C72" s="4">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="D72" s="3">
         <v>12</v>
       </c>
       <c r="E72" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="3">
-        <v>10254</v>
+        <v>10080</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C73" s="4">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="D73" s="3">
         <v>12</v>
       </c>
       <c r="E73" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="3">
-        <v>10318</v>
+        <v>10090</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="C74" s="4">
-        <v>50</v>
+        <v>7550</v>
       </c>
       <c r="D74" s="3">
         <v>12</v>
       </c>
       <c r="E74" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="3">
-        <v>10362</v>
+        <v>10254</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C75" s="4">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="D75" s="3">
         <v>12</v>
       </c>
       <c r="E75" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="3">
-        <v>10692</v>
+        <v>10318</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C76" s="4">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="D76" s="3">
         <v>12</v>
       </c>
       <c r="E76" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="3">
-        <v>10707</v>
+        <v>10362</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C77" s="4">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D77" s="3">
         <v>12</v>
       </c>
       <c r="E77" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="3">
-        <v>10725</v>
+        <v>10692</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C78" s="4">
         <v>3</v>
@@ -2184,32 +2195,32 @@
         <v>12</v>
       </c>
       <c r="E78" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="3">
-        <v>10762</v>
+        <v>10707</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C79" s="4">
-        <v>1376.8</v>
+        <v>3</v>
       </c>
       <c r="D79" s="3">
         <v>12</v>
       </c>
       <c r="E79" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="3">
-        <v>10830</v>
+        <v>10725</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C80" s="4">
         <v>3</v>
@@ -2218,185 +2229,185 @@
         <v>12</v>
       </c>
       <c r="E80" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="3">
-        <v>10832</v>
+        <v>10762</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C81" s="4">
-        <v>1015</v>
+        <v>1376.8</v>
       </c>
       <c r="D81" s="3">
         <v>12</v>
       </c>
       <c r="E81" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="3">
-        <v>10834</v>
+        <v>10830</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C82" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D82" s="3">
         <v>12</v>
       </c>
       <c r="E82" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="3">
-        <v>10836</v>
+        <v>10832</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="C83" s="4">
-        <v>5</v>
+        <v>1015</v>
       </c>
       <c r="D83" s="3">
         <v>12</v>
       </c>
       <c r="E83" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="3">
-        <v>10936</v>
+        <v>10834</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C84" s="4">
-        <v>1093.3499999999999</v>
+        <v>5</v>
       </c>
       <c r="D84" s="3">
         <v>12</v>
       </c>
       <c r="E84" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="3">
-        <v>10937</v>
+        <v>10836</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="C85" s="4">
-        <v>1183.5</v>
+        <v>5</v>
       </c>
       <c r="D85" s="3">
         <v>12</v>
       </c>
       <c r="E85" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="3">
-        <v>10997</v>
+        <v>10936</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C86" s="4">
-        <v>188.5</v>
+        <v>1093.3499999999999</v>
       </c>
       <c r="D86" s="3">
         <v>12</v>
       </c>
       <c r="E86" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="3">
-        <v>10998</v>
+        <v>10937</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C87" s="4">
-        <v>69.352999999999994</v>
+        <v>1183.5</v>
       </c>
       <c r="D87" s="3">
         <v>12</v>
       </c>
       <c r="E87" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="3">
-        <v>11003</v>
+        <v>10997</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C88" s="4">
-        <v>5</v>
+        <v>188.5</v>
       </c>
       <c r="D88" s="3">
         <v>12</v>
       </c>
       <c r="E88" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="3">
-        <v>11105</v>
+        <v>10998</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C89" s="4">
-        <v>5</v>
+        <v>69.352999999999994</v>
       </c>
       <c r="D89" s="3">
         <v>12</v>
       </c>
       <c r="E89" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="3">
-        <v>11106</v>
+        <v>11003</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C90" s="4">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D90" s="3">
         <v>12</v>
       </c>
       <c r="E90" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="3">
-        <v>11107</v>
+        <v>11105</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C91" s="4">
         <v>5</v>
@@ -2405,117 +2416,117 @@
         <v>12</v>
       </c>
       <c r="E91" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="3">
-        <v>11243</v>
+        <v>11106</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C92" s="4">
-        <v>209</v>
+        <v>20</v>
       </c>
       <c r="D92" s="3">
         <v>12</v>
       </c>
       <c r="E92" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="3">
-        <v>11269</v>
+        <v>11107</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C93" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D93" s="3">
         <v>12</v>
       </c>
       <c r="E93" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="3">
-        <v>11316</v>
+        <v>11243</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C94" s="4">
-        <v>10</v>
+        <v>209</v>
       </c>
       <c r="D94" s="3">
         <v>12</v>
       </c>
       <c r="E94" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="3">
-        <v>11318</v>
+        <v>11269</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C95" s="4">
-        <v>97.7</v>
+        <v>10</v>
       </c>
       <c r="D95" s="3">
         <v>12</v>
       </c>
       <c r="E95" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="3">
-        <v>11362</v>
+        <v>11316</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C96" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D96" s="3">
         <v>12</v>
       </c>
       <c r="E96" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="3">
-        <v>11396</v>
+        <v>11318</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C97" s="4">
-        <v>7</v>
+        <v>97.7</v>
       </c>
       <c r="D97" s="3">
         <v>12</v>
       </c>
       <c r="E97" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="3">
-        <v>11397</v>
+        <v>11362</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C98" s="4">
         <v>5</v>
@@ -2524,32 +2535,32 @@
         <v>12</v>
       </c>
       <c r="E98" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="3">
-        <v>11444</v>
+        <v>11396</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C99" s="4">
-        <v>230</v>
+        <v>7</v>
       </c>
       <c r="D99" s="3">
         <v>12</v>
       </c>
       <c r="E99" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="3">
-        <v>12497</v>
+        <v>11397</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C100" s="4">
         <v>5</v>
@@ -2558,32 +2569,32 @@
         <v>12</v>
       </c>
       <c r="E100" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" s="3">
-        <v>12498</v>
+        <v>11444</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C101" s="4">
-        <v>5</v>
+        <v>230</v>
       </c>
       <c r="D101" s="3">
         <v>12</v>
       </c>
       <c r="E101" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="3">
-        <v>12499</v>
+        <v>12497</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C102" s="4">
         <v>5</v>
@@ -2592,15 +2603,15 @@
         <v>12</v>
       </c>
       <c r="E102" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="3">
-        <v>12501</v>
+        <v>12498</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C103" s="4">
         <v>5</v>
@@ -2609,15 +2620,15 @@
         <v>12</v>
       </c>
       <c r="E103" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" s="3">
-        <v>12503</v>
+        <v>12499</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C104" s="4">
         <v>5</v>
@@ -2626,15 +2637,15 @@
         <v>12</v>
       </c>
       <c r="E104" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" s="3">
-        <v>12504</v>
+        <v>12501</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C105" s="4">
         <v>5</v>
@@ -2643,35 +2654,35 @@
         <v>12</v>
       </c>
       <c r="E105" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" s="3">
-        <v>12514</v>
+        <v>12503</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C106" s="4">
-        <v>1500.1</v>
+        <v>5</v>
       </c>
       <c r="D106" s="3">
         <v>12</v>
       </c>
       <c r="E106" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" s="3">
-        <v>12516</v>
+        <v>12504</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C107" s="4">
-        <v>2464.6</v>
+        <v>5</v>
       </c>
       <c r="D107" s="3">
         <v>12</v>
@@ -2682,112 +2693,112 @@
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="3">
-        <v>12517</v>
+        <v>12514</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C108" s="4">
-        <v>840.4</v>
+        <v>1200.0999999999999</v>
       </c>
       <c r="D108" s="3">
         <v>12</v>
       </c>
       <c r="E108" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" s="3">
-        <v>12518</v>
+        <v>12515</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="C109" s="4">
-        <v>778.5</v>
+        <v>5480</v>
       </c>
       <c r="D109" s="3">
         <v>12</v>
       </c>
       <c r="E109" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" s="3">
-        <v>12673</v>
+        <v>12516</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C110" s="4">
-        <v>5</v>
+        <v>2364.6</v>
       </c>
       <c r="D110" s="3">
         <v>12</v>
       </c>
       <c r="E110" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" s="3">
-        <v>13150</v>
+        <v>12517</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C111" s="4">
-        <v>637.20000000000005</v>
+        <v>740.4</v>
       </c>
       <c r="D111" s="3">
         <v>12</v>
       </c>
       <c r="E111" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="3">
-        <v>14365</v>
+        <v>12673</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C112" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D112" s="3">
         <v>12</v>
       </c>
       <c r="E112" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" s="3">
-        <v>14366</v>
+        <v>13150</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C113" s="4">
-        <v>2</v>
+        <v>337.2</v>
       </c>
       <c r="D113" s="3">
         <v>12</v>
       </c>
       <c r="E113" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="3">
-        <v>14367</v>
+        <v>14365</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C114" s="4">
         <v>2</v>
@@ -2796,83 +2807,83 @@
         <v>12</v>
       </c>
       <c r="E114" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="3">
-        <v>14928</v>
+        <v>14366</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C115" s="4">
-        <v>7.5</v>
+        <v>2</v>
       </c>
       <c r="D115" s="3">
         <v>12</v>
       </c>
       <c r="E115" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" s="3">
-        <v>15405</v>
+        <v>14367</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C116" s="4">
-        <v>225</v>
+        <v>2</v>
       </c>
       <c r="D116" s="3">
         <v>12</v>
       </c>
       <c r="E116" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" s="3">
-        <v>16460</v>
+        <v>14928</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C117" s="4">
-        <v>1</v>
+        <v>7.5</v>
       </c>
       <c r="D117" s="3">
         <v>12</v>
       </c>
       <c r="E117" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" s="3">
-        <v>16461</v>
+        <v>15405</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C118" s="4">
-        <v>1</v>
+        <v>225</v>
       </c>
       <c r="D118" s="3">
         <v>12</v>
       </c>
       <c r="E118" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" s="3">
-        <v>16462</v>
+        <v>16460</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C119" s="4">
         <v>1</v>
@@ -2881,38 +2892,114 @@
         <v>12</v>
       </c>
       <c r="E119" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" s="3">
+        <v>16461</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C120" s="4">
+        <v>1</v>
+      </c>
+      <c r="D120" s="3">
+        <v>12</v>
+      </c>
+      <c r="E120" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A121" s="3">
+        <v>16462</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C121" s="4">
+        <v>1</v>
+      </c>
+      <c r="D121" s="3">
+        <v>12</v>
+      </c>
+      <c r="E121" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A122" s="3">
+        <v>17075</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C122" s="4">
+        <v>5230</v>
+      </c>
+      <c r="D122" s="3">
+        <v>12</v>
+      </c>
+      <c r="E122" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A123" s="3">
         <v>17076</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C120" s="4">
-        <v>540.79999999999995</v>
-      </c>
-      <c r="D120" s="3">
-        <v>12</v>
-      </c>
-      <c r="E120" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A121" s="3"/>
-      <c r="B121" s="1"/>
-      <c r="C121" s="4"/>
-      <c r="D121" s="3"/>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A122" s="3"/>
-      <c r="B122" s="1"/>
-      <c r="C122" s="4"/>
+      <c r="B123" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C123" s="4">
+        <v>140.80000000000001</v>
+      </c>
+      <c r="D123" s="3">
+        <v>12</v>
+      </c>
+      <c r="E123" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A124" s="3">
+        <v>30189</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C124" s="4">
+        <v>500</v>
+      </c>
+      <c r="D124" s="3">
+        <v>12</v>
+      </c>
+      <c r="E124" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A125" s="3"/>
+      <c r="B125" s="1"/>
+      <c r="C125" s="4"/>
+      <c r="D125" s="3"/>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A126" s="3"/>
+      <c r="B126" s="1"/>
+      <c r="C126" s="4"/>
+      <c r="D126" s="3"/>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A127" s="3"/>
+      <c r="B127" s="1"/>
+      <c r="C127" s="4"/>
+      <c r="D127" s="3"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E120" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="9999" orientation="landscape"/>
